--- a/AAII_Financials/Quarterly/GV_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GV_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Quarterly/GV_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GV_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="92">
   <si>
     <t>GV</t>
   </si>
@@ -656,328 +656,341 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45016</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44834</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44651</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44469</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44286</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44104</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K7" s="2">
+      <c r="K7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L7" s="2">
         <v>43921</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>43830</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>43738</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>43646</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>43555</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>43465</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43373</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43281</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43190</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43100</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43008</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>42916</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>42825</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>42735</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E8" s="3">
         <v>6600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>7700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2000</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K8" s="3">
+      <c r="K8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L8" s="3">
         <v>44800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>44100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>44700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>44400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>47500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>36700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>29500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>37500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>34400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>29600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>24500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>29100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>30700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>31800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>30700</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E9" s="3">
         <v>3800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>900</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K9" s="3">
+      <c r="K9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L9" s="3">
         <v>37700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>34200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>37800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>37700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>39500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>31800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>26100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>30100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>27000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>24500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>20900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>21600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>22900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>24400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>23800</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E10" s="3">
         <v>2800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>4200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1100</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K10" s="3">
+      <c r="K10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L10" s="3">
         <v>7100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>9900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>6900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>6700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>8000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>4900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>3400</v>
-      </c>
-      <c r="R10" s="3">
-        <v>7400</v>
       </c>
       <c r="S10" s="3">
         <v>7400</v>
       </c>
       <c r="T10" s="3">
+        <v>7400</v>
+      </c>
+      <c r="U10" s="3">
         <v>5100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>3600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>7500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>7800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>7400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1003,8 +1016,9 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1074,8 +1088,11 @@
       <c r="Y12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1145,34 +1162,37 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>100</v>
-      </c>
-      <c r="E14" s="3">
-        <v>-100</v>
       </c>
       <c r="F14" s="3">
         <v>-100</v>
       </c>
       <c r="G14" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H14" s="3">
         <v>-400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-100</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1216,8 +1236,11 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1243,34 +1266,34 @@
         <v>0</v>
       </c>
       <c r="K15" s="3">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3">
         <v>2900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2800</v>
-      </c>
-      <c r="M15" s="3">
-        <v>2700</v>
       </c>
       <c r="N15" s="3">
         <v>2700</v>
       </c>
       <c r="O15" s="3">
+        <v>2700</v>
+      </c>
+      <c r="P15" s="3">
         <v>2600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>2400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>2100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>2000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>1900</v>
-      </c>
-      <c r="T15" s="3">
-        <v>1800</v>
       </c>
       <c r="U15" s="3">
         <v>1800</v>
@@ -1279,16 +1302,19 @@
         <v>1800</v>
       </c>
       <c r="W15" s="3">
+        <v>1800</v>
+      </c>
+      <c r="X15" s="3">
         <v>1700</v>
-      </c>
-      <c r="X15" s="3">
-        <v>1600</v>
       </c>
       <c r="Y15" s="3">
         <v>1600</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1311,150 +1337,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E17" s="3">
         <v>5500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1000</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K17" s="3">
+      <c r="K17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L17" s="3">
         <v>43200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>39500</v>
-      </c>
-      <c r="M17" s="3">
-        <v>42700</v>
       </c>
       <c r="N17" s="3">
         <v>42700</v>
       </c>
       <c r="O17" s="3">
+        <v>42700</v>
+      </c>
+      <c r="P17" s="3">
         <v>44600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>35800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>29600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>34100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>31000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>28000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>24400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>25000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>26400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>27300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>26900</v>
       </c>
     </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E18" s="3">
         <v>1100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>3800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1000</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K18" s="3">
+      <c r="K18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L18" s="3">
         <v>1600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>4600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-100</v>
-      </c>
-      <c r="R18" s="3">
-        <v>3400</v>
       </c>
       <c r="S18" s="3">
         <v>3400</v>
       </c>
       <c r="T18" s="3">
+        <v>3400</v>
+      </c>
+      <c r="U18" s="3">
         <v>1600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>4100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>4300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>4500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1480,44 +1513,45 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E20" s="3">
         <v>-400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>100</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="I20" s="3">
         <v>300</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="J20" s="3">
+        <v>300</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
@@ -1525,17 +1559,17 @@
         <v>0</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>100</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
         <v>0</v>
       </c>
@@ -1551,8 +1585,11 @@
       <c r="Y20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1562,100 +1599,103 @@
       <c r="E21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F21" s="3">
+      <c r="F21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G21" s="3">
         <v>1700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>4100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1300</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K21" s="3">
+      <c r="K21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L21" s="3">
         <v>4600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>7400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>4900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>4500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>5500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2100</v>
-      </c>
-      <c r="R21" s="3">
-        <v>5400</v>
       </c>
       <c r="S21" s="3">
         <v>5400</v>
       </c>
       <c r="T21" s="3">
+        <v>5400</v>
+      </c>
+      <c r="U21" s="3">
         <v>3500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>5900</v>
-      </c>
-      <c r="W21" s="3">
-        <v>6100</v>
       </c>
       <c r="X21" s="3">
         <v>6100</v>
       </c>
       <c r="Y21" s="3">
+        <v>6100</v>
+      </c>
+      <c r="Z21" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E22" s="3">
         <v>2400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>100</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K22" s="3">
-        <v>300</v>
+      <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L22" s="3">
         <v>300</v>
       </c>
       <c r="M22" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="N22" s="3">
         <v>400</v>
@@ -1664,10 +1704,10 @@
         <v>400</v>
       </c>
       <c r="P22" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q22" s="3">
         <v>300</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>200</v>
       </c>
       <c r="R22" s="3">
         <v>200</v>
@@ -1682,7 +1722,7 @@
         <v>200</v>
       </c>
       <c r="V22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="W22" s="3">
         <v>100</v>
@@ -1693,150 +1733,159 @@
       <c r="Y22" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>3900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1200</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K23" s="3">
+      <c r="K23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L23" s="3">
         <v>1400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>4300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>3200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>3300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1500</v>
       </c>
-      <c r="U23" s="3">
-        <v>0</v>
-      </c>
       <c r="V23" s="3">
+        <v>0</v>
+      </c>
+      <c r="W23" s="3">
         <v>4000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>4200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>4300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E24" s="3">
         <v>-1000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>100</v>
-      </c>
-      <c r="F24" s="3">
-        <v>300</v>
       </c>
       <c r="G24" s="3">
         <v>300</v>
       </c>
       <c r="H24" s="3">
+        <v>300</v>
+      </c>
+      <c r="I24" s="3">
         <v>1000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>300</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K24" s="3">
+      <c r="K24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L24" s="3">
         <v>-100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>800</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
       <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>-100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>500</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
       <c r="V24" s="3">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="W24" s="3">
         <v>1500</v>
       </c>
       <c r="X24" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Y24" s="3">
         <v>1700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1906,150 +1955,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-2800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>2900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>900</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K26" s="3">
+      <c r="K26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L26" s="3">
         <v>1500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-2700</v>
       </c>
-      <c r="F27" s="3">
-        <v>0</v>
-      </c>
       <c r="G27" s="3">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3">
         <v>600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>2900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>900</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K27" s="3">
+      <c r="K27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L27" s="3">
         <v>1500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>3000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>2500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2119,8 +2177,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2145,8 +2206,8 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>8</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>8</v>
@@ -2160,27 +2221,27 @@
       <c r="O29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P29" s="3">
-        <v>0</v>
+      <c r="P29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>8</v>
+      <c r="R29" s="3">
+        <v>0</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T29" s="3">
+      <c r="T29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U29" s="3">
         <v>2300</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-100</v>
       </c>
-      <c r="V29" s="3">
-        <v>0</v>
-      </c>
       <c r="W29" s="3">
         <v>0</v>
       </c>
@@ -2190,8 +2251,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2261,8 +2325,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2332,44 +2399,47 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="E32" s="3">
         <v>400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-100</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="I32" s="3">
         <v>-300</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="J32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
@@ -2377,17 +2447,17 @@
         <v>0</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>-100</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
         <v>0</v>
       </c>
@@ -2403,79 +2473,85 @@
       <c r="Y32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-2700</v>
       </c>
-      <c r="F33" s="3">
-        <v>0</v>
-      </c>
       <c r="G33" s="3">
+        <v>0</v>
+      </c>
+      <c r="H33" s="3">
         <v>600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>2900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>900</v>
       </c>
-      <c r="J33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K33" s="3">
+      <c r="K33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L33" s="3">
         <v>1500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>3000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>3300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2545,155 +2621,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-2700</v>
       </c>
-      <c r="F35" s="3">
-        <v>0</v>
-      </c>
       <c r="G35" s="3">
+        <v>0</v>
+      </c>
+      <c r="H35" s="3">
         <v>600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>2900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>900</v>
       </c>
-      <c r="J35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K35" s="3">
+      <c r="K35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L35" s="3">
         <v>1500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>3000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>3300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45016</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44834</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44651</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44469</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44286</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44104</v>
       </c>
-      <c r="J38" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K38" s="2">
+      <c r="K38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L38" s="2">
         <v>43921</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>43830</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>43738</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>43646</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>43555</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>43465</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43373</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43281</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43190</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43100</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43008</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>42916</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>42825</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>42735</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2719,8 +2804,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2746,79 +2832,83 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>400</v>
+      </c>
+      <c r="E41" s="3">
         <v>700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>300</v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I41" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J41" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K41" s="3">
+      <c r="K41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L41" s="3">
         <v>27000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>23300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>20600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>15500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>15000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>11400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>13600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>9900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>16600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>18500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>20400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>22400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>14200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>20600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>16800</v>
       </c>
     </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2834,8 +2924,8 @@
       <c r="G42" s="3">
         <v>100</v>
       </c>
-      <c r="H42" s="3" t="s">
-        <v>8</v>
+      <c r="H42" s="3">
+        <v>100</v>
       </c>
       <c r="I42" s="3" t="s">
         <v>8</v>
@@ -2843,8 +2933,8 @@
       <c r="J42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
+      <c r="K42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L42" s="3">
         <v>0</v>
@@ -2888,8 +2978,11 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2900,67 +2993,70 @@
         <v>300</v>
       </c>
       <c r="F43" s="3">
+        <v>300</v>
+      </c>
+      <c r="G43" s="3">
         <v>600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1400</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I43" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K43" s="3">
+      <c r="K43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L43" s="3">
         <v>44000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>34700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>37800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>39200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>42400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>35500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>33400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>34800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>30200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>22200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>20000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>19300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>17000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>19600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>19200</v>
       </c>
     </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2970,39 +3066,39 @@
       <c r="E44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F44" s="3">
-        <v>0</v>
+      <c r="F44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G44" s="3">
+        <v>0</v>
+      </c>
+      <c r="H44" s="3">
         <v>200</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I44" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K44" s="3">
+      <c r="K44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L44" s="3">
         <v>1000</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N44" s="3">
+      <c r="N44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O44" s="3">
         <v>1000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>5100</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q44" s="3" t="s">
         <v>8</v>
       </c>
@@ -3012,194 +3108,203 @@
       <c r="S44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T44" s="3">
+      <c r="T44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U44" s="3">
         <v>6100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>7300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>6400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>10400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>7300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>12000</v>
       </c>
     </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E45" s="3">
         <v>21400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>300</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L45" s="3">
         <v>2200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3000</v>
-      </c>
-      <c r="M45" s="3">
-        <v>2700</v>
       </c>
       <c r="N45" s="3">
         <v>2700</v>
       </c>
       <c r="O45" s="3">
+        <v>2700</v>
+      </c>
+      <c r="P45" s="3">
         <v>2600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>10700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>9000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>6800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>6300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>4900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>5200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>4300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>4600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>3900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E46" s="3">
         <v>22300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2300</v>
       </c>
-      <c r="H46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I46" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J46" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K46" s="3">
+      <c r="K46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L46" s="3">
         <v>74200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>61000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>61200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>58400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>65300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>57600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>55900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>51500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>53100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>51700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>52900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>52400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>46200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>51400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>52800</v>
       </c>
     </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E47" s="3">
         <v>800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>7400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2500</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I47" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -3243,79 +3348,85 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>68700</v>
+      </c>
+      <c r="E48" s="3">
         <v>70300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>90100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>24200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>23000</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K48" s="3">
+      <c r="K48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L48" s="3">
         <v>68600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>61900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>60900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>61600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>59800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>48900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>47500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>40200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>38400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>36100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>37200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>37300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>37400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>33200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>32800</v>
       </c>
     </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3326,22 +3437,22 @@
         <v>1900</v>
       </c>
       <c r="F49" s="3">
+        <v>1900</v>
+      </c>
+      <c r="G49" s="3">
         <v>2100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>700</v>
       </c>
-      <c r="H49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I49" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K49" s="3">
-        <v>700</v>
+      <c r="K49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L49" s="3">
         <v>700</v>
@@ -3350,7 +3461,7 @@
         <v>700</v>
       </c>
       <c r="N49" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="O49" s="3">
         <v>800</v>
@@ -3368,7 +3479,7 @@
         <v>800</v>
       </c>
       <c r="T49" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="U49" s="3">
         <v>900</v>
@@ -3385,8 +3496,11 @@
       <c r="Y49" s="3">
         <v>900</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3456,8 +3570,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3527,25 +3644,28 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>200</v>
+      </c>
+      <c r="E52" s="3">
         <v>900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1000</v>
       </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>8</v>
+      <c r="H52" s="3">
+        <v>0</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>8</v>
@@ -3553,53 +3673,56 @@
       <c r="J52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K52" s="3">
-        <v>5700</v>
+      <c r="K52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L52" s="3">
         <v>5700</v>
       </c>
       <c r="M52" s="3">
-        <v>5600</v>
+        <v>5700</v>
       </c>
       <c r="N52" s="3">
         <v>5600</v>
       </c>
       <c r="O52" s="3">
+        <v>5600</v>
+      </c>
+      <c r="P52" s="3">
         <v>5100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>5300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>5700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>5600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>5400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>5000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>5500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>5800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>5300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>5700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3669,79 +3792,85 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>91600</v>
+      </c>
+      <c r="E54" s="3">
         <v>96200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>94000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>36200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>28500</v>
       </c>
-      <c r="H54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I54" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J54" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K54" s="3">
+      <c r="K54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L54" s="3">
         <v>149200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>129400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>128300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>126400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>131000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>112500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>109800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>98200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>97700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>93600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>96500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>96300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>89700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>91300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>89900</v>
       </c>
     </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3767,8 +3896,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3794,96 +3924,100 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>900</v>
+      </c>
+      <c r="E57" s="3">
         <v>1000</v>
-      </c>
-      <c r="E57" s="3">
-        <v>300</v>
       </c>
       <c r="F57" s="3">
         <v>300</v>
       </c>
       <c r="G57" s="3">
+        <v>300</v>
+      </c>
+      <c r="H57" s="3">
         <v>100</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I57" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K57" s="3">
+      <c r="K57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L57" s="3">
         <v>15200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>13900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>16100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>13500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>15400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>16000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>16600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>11400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>12000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>9400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>9000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>7700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>8100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>11400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>11700</v>
       </c>
     </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>48200</v>
+      </c>
+      <c r="E58" s="3">
         <v>49400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1800</v>
-      </c>
-      <c r="F58" s="3">
-        <v>500</v>
       </c>
       <c r="G58" s="3">
         <v>500</v>
       </c>
-      <c r="H58" s="3" t="s">
-        <v>8</v>
+      <c r="H58" s="3">
+        <v>500</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>8</v>
@@ -3891,35 +4025,35 @@
       <c r="J58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K58" s="3">
+      <c r="K58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L58" s="3">
         <v>8900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>7800</v>
-      </c>
-      <c r="M58" s="3">
-        <v>7600</v>
       </c>
       <c r="N58" s="3">
         <v>7600</v>
       </c>
       <c r="O58" s="3">
+        <v>7600</v>
+      </c>
+      <c r="P58" s="3">
         <v>12400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>7300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>7000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>5200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>6200</v>
-      </c>
-      <c r="T58" s="3">
-        <v>6100</v>
       </c>
       <c r="U58" s="3">
         <v>6100</v>
@@ -3936,61 +4070,64 @@
       <c r="Y58" s="3">
         <v>6100</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3">
+        <v>6100</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>20500</v>
+      </c>
+      <c r="E59" s="3">
         <v>30100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>16400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>12500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5800</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I59" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L59" s="3">
         <v>3000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>500</v>
-      </c>
-      <c r="T59" s="3">
-        <v>300</v>
       </c>
       <c r="U59" s="3">
         <v>300</v>
@@ -3999,105 +4136,111 @@
         <v>300</v>
       </c>
       <c r="W59" s="3">
+        <v>300</v>
+      </c>
+      <c r="X59" s="3">
         <v>1800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>69600</v>
+      </c>
+      <c r="E60" s="3">
         <v>80500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>18500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>13300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6300</v>
       </c>
-      <c r="H60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I60" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J60" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K60" s="3">
+      <c r="K60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L60" s="3">
         <v>27000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>24300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>26900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>25000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>31700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>24500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>24000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>17200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>18800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>15700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>15400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>14100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>16000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>18400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>18200</v>
       </c>
     </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>500</v>
+      </c>
+      <c r="E61" s="3">
         <v>700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>59900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>18300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>18200</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
       <c r="I61" s="3">
         <v>0</v>
       </c>
@@ -4105,69 +4248,72 @@
         <v>0</v>
       </c>
       <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
         <v>35800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>24400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>26400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>28400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>30400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>21900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>18700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>14400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>14900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>16200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>18900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>20400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>14700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>16200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>18300</v>
       </c>
     </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>600</v>
+      </c>
+      <c r="E62" s="3">
         <v>2300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1000</v>
       </c>
-      <c r="G62" s="3">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>8</v>
+      <c r="H62" s="3">
+        <v>0</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>8</v>
@@ -4175,53 +4321,56 @@
       <c r="J62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L62" s="3">
         <v>18700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>14500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>11800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>10900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>7600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>6500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>6200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>5400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>5100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>5200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>8900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>8400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>8100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>8400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>7700</v>
       </c>
     </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4291,8 +4440,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4362,8 +4514,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4433,79 +4588,85 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>70700</v>
+      </c>
+      <c r="E66" s="3">
         <v>83500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>80600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>32800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>24500</v>
       </c>
-      <c r="H66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I66" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J66" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K66" s="3">
+      <c r="K66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L66" s="3">
         <v>81500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>63200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>65100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>64300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>69700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>52900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>48900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>37100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>38800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>37100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>43200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>42900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>38800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>43100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>44200</v>
       </c>
     </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4531,8 +4692,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4602,8 +4764,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4673,8 +4838,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4744,8 +4912,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4815,79 +4986,85 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3200</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I72" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L72" s="3">
         <v>49800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>48300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>45400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>44200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>43400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>41600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>41000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>41200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>39000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>36600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>33300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>33500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>31000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>28300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>25700</v>
       </c>
     </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4957,8 +5134,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5028,8 +5208,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5099,79 +5282,85 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>20900</v>
+      </c>
+      <c r="E76" s="3">
         <v>12700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>13400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3900</v>
       </c>
-      <c r="H76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I76" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J76" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K76" s="3">
+      <c r="K76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L76" s="3">
         <v>67700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>66200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>63200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>62000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>61200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>59600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>60900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>61100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>59000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>56500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>53300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>53400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>50900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>48300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>45700</v>
       </c>
     </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5241,155 +5430,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45016</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44834</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44651</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44469</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44286</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44104</v>
       </c>
-      <c r="J80" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K80" s="2">
+      <c r="K80" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L80" s="2">
         <v>43921</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>43830</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>43738</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>43646</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>43555</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>43465</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43373</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43281</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43190</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43100</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43008</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>42916</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>42825</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>42735</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-2700</v>
       </c>
-      <c r="F81" s="3">
-        <v>0</v>
-      </c>
       <c r="G81" s="3">
+        <v>0</v>
+      </c>
+      <c r="H81" s="3">
         <v>600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>2900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>900</v>
       </c>
-      <c r="J81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K81" s="3">
+      <c r="K81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L81" s="3">
         <v>1500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>3000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>3300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5415,8 +5613,9 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5426,50 +5625,50 @@
       <c r="E83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F83" s="3">
+      <c r="F83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G83" s="3">
         <v>500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>100</v>
       </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K83" s="3">
+      <c r="J83" s="3">
+        <v>0</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L83" s="3">
         <v>2900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2800</v>
-      </c>
-      <c r="M83" s="3">
-        <v>2700</v>
       </c>
       <c r="N83" s="3">
         <v>2700</v>
       </c>
       <c r="O83" s="3">
+        <v>2700</v>
+      </c>
+      <c r="P83" s="3">
         <v>2600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>2400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>2100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>2000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1900</v>
-      </c>
-      <c r="T83" s="3">
-        <v>1800</v>
       </c>
       <c r="U83" s="3">
         <v>1800</v>
@@ -5478,16 +5677,19 @@
         <v>1800</v>
       </c>
       <c r="W83" s="3">
+        <v>1800</v>
+      </c>
+      <c r="X83" s="3">
         <v>1700</v>
-      </c>
-      <c r="X83" s="3">
-        <v>1600</v>
       </c>
       <c r="Y83" s="3">
         <v>1600</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5557,8 +5759,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5628,8 +5833,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5699,8 +5907,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5770,8 +5981,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5841,79 +6055,85 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E89" s="3">
         <v>700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>6400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>4400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2200</v>
       </c>
-      <c r="J89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K89" s="3">
+      <c r="K89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L89" s="3">
         <v>-3900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>8000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>8800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>9100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>4200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-1100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>2900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>3800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>7700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>6000</v>
       </c>
     </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5939,8 +6159,9 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5966,52 +6187,55 @@
         <v>0</v>
       </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-5000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-12400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-7500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-3400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-12000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-2100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6081,8 +6305,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6152,79 +6379,85 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>11600</v>
+      </c>
+      <c r="E94" s="3">
         <v>2500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-66000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-24300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-16300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-900</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K94" s="3">
+      <c r="K94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L94" s="3">
         <v>-4900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-12300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-4400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-6700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-4100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-3300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-6000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6250,8 +6483,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6321,8 +6555,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6392,8 +6629,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6463,8 +6703,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6534,79 +6777,85 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>66400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>17500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>13600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1200</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K100" s="3">
+      <c r="K100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L100" s="3">
         <v>12600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-6800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>13500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>6100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-2700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>5700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-2600</v>
       </c>
     </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6614,7 +6863,7 @@
         <v>-300</v>
       </c>
       <c r="E101" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="F101" s="3">
         <v>0</v>
@@ -6623,16 +6872,16 @@
         <v>0</v>
       </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>100</v>
       </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -6676,75 +6925,81 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E102" s="3">
         <v>400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>200</v>
       </c>
-      <c r="J102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K102" s="3">
+      <c r="K102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L102" s="3">
         <v>3700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>5100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>3700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>3600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-6700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-2000</v>
-      </c>
-      <c r="T102" s="3">
-        <v>-1900</v>
       </c>
       <c r="U102" s="3">
         <v>-1900</v>
       </c>
       <c r="V102" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="W102" s="3">
         <v>8100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-6400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>3800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>1800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GV_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GV_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="92">
   <si>
     <t>GV</t>
   </si>
@@ -656,341 +656,354 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44834</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44651</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44469</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44286</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44104</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L7" s="2">
+      <c r="L7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M7" s="2">
         <v>43921</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>43830</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>43738</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>43646</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>43555</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43465</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43373</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43281</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43190</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43100</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43008</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>42916</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>42825</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>42735</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E8" s="3">
         <v>5000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>6600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>7700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2000</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L8" s="3">
+      <c r="L8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M8" s="3">
         <v>44800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>44100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>44700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>44400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>47500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>36700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>29500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>37500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>34400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>29600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>24500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>29100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>30700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>31800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>30700</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E9" s="3">
         <v>3300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>900</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L9" s="3">
+      <c r="L9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M9" s="3">
         <v>37700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>34200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>37800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>37700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>39500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>31800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>26100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>30100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>27000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>24500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>20900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>21600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>22900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>24400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>23800</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>800</v>
+      </c>
+      <c r="E10" s="3">
         <v>1700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>4200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1100</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L10" s="3">
+      <c r="L10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M10" s="3">
         <v>7100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>9900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>6900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>6700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>8000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>4900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>3400</v>
-      </c>
-      <c r="S10" s="3">
-        <v>7400</v>
       </c>
       <c r="T10" s="3">
         <v>7400</v>
       </c>
       <c r="U10" s="3">
+        <v>7400</v>
+      </c>
+      <c r="V10" s="3">
         <v>5100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>3600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>7500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>7800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>7400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1017,8 +1030,9 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1091,8 +1105,11 @@
       <c r="Z12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1165,8 +1182,11 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1174,28 +1194,28 @@
         <v>0</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>100</v>
-      </c>
-      <c r="F14" s="3">
-        <v>-100</v>
       </c>
       <c r="G14" s="3">
         <v>-100</v>
       </c>
       <c r="H14" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I14" s="3">
         <v>-400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-100</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1239,8 +1259,11 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1269,34 +1292,34 @@
         <v>0</v>
       </c>
       <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3">
         <v>2900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>2800</v>
-      </c>
-      <c r="N15" s="3">
-        <v>2700</v>
       </c>
       <c r="O15" s="3">
         <v>2700</v>
       </c>
       <c r="P15" s="3">
+        <v>2700</v>
+      </c>
+      <c r="Q15" s="3">
         <v>2600</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>2400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>2100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>2000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>1900</v>
-      </c>
-      <c r="U15" s="3">
-        <v>1800</v>
       </c>
       <c r="V15" s="3">
         <v>1800</v>
@@ -1305,16 +1328,19 @@
         <v>1800</v>
       </c>
       <c r="X15" s="3">
+        <v>1800</v>
+      </c>
+      <c r="Y15" s="3">
         <v>1700</v>
-      </c>
-      <c r="Y15" s="3">
-        <v>1600</v>
       </c>
       <c r="Z15" s="3">
         <v>1600</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1338,156 +1364,163 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E17" s="3">
         <v>6900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>5500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1000</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L17" s="3">
+      <c r="L17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M17" s="3">
         <v>43200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>39500</v>
-      </c>
-      <c r="N17" s="3">
-        <v>42700</v>
       </c>
       <c r="O17" s="3">
         <v>42700</v>
       </c>
       <c r="P17" s="3">
+        <v>42700</v>
+      </c>
+      <c r="Q17" s="3">
         <v>44600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>35800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>29600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>34100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>31000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>28000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>24400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>25000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>26400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>27300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>26900</v>
       </c>
     </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>3800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1000</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L18" s="3">
+      <c r="L18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M18" s="3">
         <v>1600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>4600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-100</v>
-      </c>
-      <c r="S18" s="3">
-        <v>3400</v>
       </c>
       <c r="T18" s="3">
         <v>3400</v>
       </c>
       <c r="U18" s="3">
+        <v>3400</v>
+      </c>
+      <c r="V18" s="3">
         <v>1600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>4100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>4300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>4500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1514,47 +1547,48 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
         <v>9700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>100</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3">
         <v>300</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L20" s="3">
+      <c r="K20" s="3">
+        <v>300</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
@@ -1562,17 +1596,17 @@
         <v>0</v>
       </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>100</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
         <v>0</v>
       </c>
@@ -1588,8 +1622,11 @@
       <c r="Z20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1602,103 +1639,106 @@
       <c r="F21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G21" s="3">
+      <c r="G21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H21" s="3">
         <v>1700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>4100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1300</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L21" s="3">
+      <c r="L21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M21" s="3">
         <v>4600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>7400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>4900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>4500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>5500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>3300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2100</v>
-      </c>
-      <c r="S21" s="3">
-        <v>5400</v>
       </c>
       <c r="T21" s="3">
         <v>5400</v>
       </c>
       <c r="U21" s="3">
+        <v>5400</v>
+      </c>
+      <c r="V21" s="3">
         <v>3500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>5900</v>
-      </c>
-      <c r="X21" s="3">
-        <v>6100</v>
       </c>
       <c r="Y21" s="3">
         <v>6100</v>
       </c>
       <c r="Z21" s="3">
+        <v>6100</v>
+      </c>
+      <c r="AA21" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E22" s="3">
         <v>2800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>2400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>100</v>
       </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L22" s="3">
-        <v>300</v>
+      <c r="K22" s="3">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M22" s="3">
         <v>300</v>
       </c>
       <c r="N22" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="O22" s="3">
         <v>400</v>
@@ -1707,10 +1747,10 @@
         <v>400</v>
       </c>
       <c r="Q22" s="3">
+        <v>400</v>
+      </c>
+      <c r="R22" s="3">
         <v>300</v>
-      </c>
-      <c r="R22" s="3">
-        <v>200</v>
       </c>
       <c r="S22" s="3">
         <v>200</v>
@@ -1725,7 +1765,7 @@
         <v>200</v>
       </c>
       <c r="W22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="X22" s="3">
         <v>100</v>
@@ -1736,156 +1776,165 @@
       <c r="Z22" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E23" s="3">
         <v>5000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-2700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>3900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1200</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L23" s="3">
+      <c r="L23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M23" s="3">
         <v>1400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>4300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>3200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>3300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1500</v>
       </c>
-      <c r="V23" s="3">
-        <v>0</v>
-      </c>
       <c r="W23" s="3">
+        <v>0</v>
+      </c>
+      <c r="X23" s="3">
         <v>4000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>4200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>4300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E24" s="3">
         <v>1100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-1000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>100</v>
-      </c>
-      <c r="G24" s="3">
-        <v>300</v>
       </c>
       <c r="H24" s="3">
         <v>300</v>
       </c>
       <c r="I24" s="3">
+        <v>300</v>
+      </c>
+      <c r="J24" s="3">
         <v>1000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>300</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L24" s="3">
+      <c r="L24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M24" s="3">
         <v>-100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>800</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
       <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
         <v>-100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>500</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
       <c r="W24" s="3">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="X24" s="3">
         <v>1500</v>
       </c>
       <c r="Y24" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Z24" s="3">
         <v>1700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1958,156 +2007,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E26" s="3">
         <v>4000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-2800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>900</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L26" s="3">
+      <c r="L26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M26" s="3">
         <v>1500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>2600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E27" s="3">
         <v>4000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-2700</v>
       </c>
-      <c r="G27" s="3">
-        <v>0</v>
-      </c>
       <c r="H27" s="3">
+        <v>0</v>
+      </c>
+      <c r="I27" s="3">
         <v>600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>900</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L27" s="3">
+      <c r="L27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M27" s="3">
         <v>1500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>3000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>2600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2180,8 +2238,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2209,8 +2270,8 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>8</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>8</v>
@@ -2224,27 +2285,27 @@
       <c r="P29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>8</v>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U29" s="3">
+      <c r="U29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V29" s="3">
         <v>2300</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-100</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
       <c r="X29" s="3">
         <v>0</v>
       </c>
@@ -2254,8 +2315,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2328,8 +2392,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2402,47 +2469,50 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
         <v>-9700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-100</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="J32" s="3">
         <v>-300</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L32" s="3">
+      <c r="K32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
@@ -2450,17 +2520,17 @@
         <v>0</v>
       </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>-100</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
         <v>0</v>
       </c>
@@ -2476,82 +2546,88 @@
       <c r="Z32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E33" s="3">
         <v>4000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-2700</v>
       </c>
-      <c r="G33" s="3">
-        <v>0</v>
-      </c>
       <c r="H33" s="3">
+        <v>0</v>
+      </c>
+      <c r="I33" s="3">
         <v>600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>900</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L33" s="3">
+      <c r="L33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M33" s="3">
         <v>1500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>3300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>2600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2624,161 +2700,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E35" s="3">
         <v>4000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-2700</v>
       </c>
-      <c r="G35" s="3">
-        <v>0</v>
-      </c>
       <c r="H35" s="3">
+        <v>0</v>
+      </c>
+      <c r="I35" s="3">
         <v>600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>900</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L35" s="3">
+      <c r="L35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M35" s="3">
         <v>1500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>3300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>2600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44834</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44651</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44469</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44286</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44104</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L38" s="2">
+      <c r="L38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M38" s="2">
         <v>43921</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>43830</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>43738</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>43646</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>43555</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43465</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43373</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43281</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43190</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43100</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43008</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>42916</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>42825</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>42735</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2805,8 +2890,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2833,87 +2919,91 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>600</v>
+      </c>
+      <c r="E41" s="3">
         <v>400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>300</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J41" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L41" s="3">
+      <c r="L41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M41" s="3">
         <v>27000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>23300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>20600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>15500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>15000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>11400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>13600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>9900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>16600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>18500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>20400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>22400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>14200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>20600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>16800</v>
       </c>
     </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
         <v>100</v>
@@ -2927,8 +3017,8 @@
       <c r="H42" s="3">
         <v>100</v>
       </c>
-      <c r="I42" s="3" t="s">
-        <v>8</v>
+      <c r="I42" s="3">
+        <v>100</v>
       </c>
       <c r="J42" s="3" t="s">
         <v>8</v>
@@ -2936,8 +3026,8 @@
       <c r="K42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
+      <c r="L42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M42" s="3">
         <v>0</v>
@@ -2981,13 +3071,16 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="E43" s="3">
         <v>300</v>
@@ -2996,67 +3089,70 @@
         <v>300</v>
       </c>
       <c r="G43" s="3">
+        <v>300</v>
+      </c>
+      <c r="H43" s="3">
         <v>600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1400</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L43" s="3">
+      <c r="L43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M43" s="3">
         <v>44000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>34700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>37800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>39200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>42400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>35500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>33400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>34800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>30200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>22200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>20000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>19300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>17000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>19600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>19200</v>
       </c>
     </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3069,39 +3165,39 @@
       <c r="F44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G44" s="3">
-        <v>0</v>
+      <c r="G44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H44" s="3">
+        <v>0</v>
+      </c>
+      <c r="I44" s="3">
         <v>200</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J44" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L44" s="3">
+      <c r="L44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M44" s="3">
         <v>1000</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O44" s="3">
+      <c r="O44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P44" s="3">
         <v>1000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>5100</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R44" s="3" t="s">
         <v>8</v>
       </c>
@@ -3111,203 +3207,212 @@
       <c r="T44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U44" s="3">
+      <c r="U44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V44" s="3">
         <v>6100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>7300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>6400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>10400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>7300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>12000</v>
       </c>
     </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E45" s="3">
         <v>17600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>21400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>300</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M45" s="3">
         <v>2200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3000</v>
-      </c>
-      <c r="N45" s="3">
-        <v>2700</v>
       </c>
       <c r="O45" s="3">
         <v>2700</v>
       </c>
       <c r="P45" s="3">
+        <v>2700</v>
+      </c>
+      <c r="Q45" s="3">
         <v>2600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>10700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>9000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>6800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>6300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>4900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>5200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>4300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>4600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>3900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E46" s="3">
         <v>18300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>22300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2300</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J46" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L46" s="3">
+      <c r="L46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M46" s="3">
         <v>74200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>61000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>61200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>58400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>65300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>57600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>55900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>51500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>53100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>51700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>52900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>52400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>46200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>51400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>52800</v>
       </c>
     </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>0</v>
+      </c>
+      <c r="E47" s="3">
         <v>2400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>7400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2500</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -3351,82 +3456,88 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>83600</v>
+      </c>
+      <c r="E48" s="3">
         <v>68700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>70300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>90100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>24200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>23000</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L48" s="3">
+      <c r="L48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M48" s="3">
         <v>68600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>61900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>60900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>61600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>59800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>48900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>47500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>40200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>38400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>36100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>37200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>37300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>37400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>33200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>32800</v>
       </c>
     </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3440,22 +3551,22 @@
         <v>1900</v>
       </c>
       <c r="G49" s="3">
+        <v>1900</v>
+      </c>
+      <c r="H49" s="3">
         <v>2100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>700</v>
       </c>
-      <c r="I49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J49" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L49" s="3">
-        <v>700</v>
+      <c r="L49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M49" s="3">
         <v>700</v>
@@ -3464,7 +3575,7 @@
         <v>700</v>
       </c>
       <c r="O49" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="P49" s="3">
         <v>800</v>
@@ -3482,7 +3593,7 @@
         <v>800</v>
       </c>
       <c r="U49" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="V49" s="3">
         <v>900</v>
@@ -3499,8 +3610,11 @@
       <c r="Z49" s="3">
         <v>900</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3573,8 +3687,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3647,28 +3764,31 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>300</v>
+      </c>
+      <c r="E52" s="3">
         <v>200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1000</v>
       </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>8</v>
+      <c r="I52" s="3">
+        <v>0</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>8</v>
@@ -3676,53 +3796,56 @@
       <c r="K52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L52" s="3">
-        <v>5700</v>
+      <c r="L52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M52" s="3">
         <v>5700</v>
       </c>
       <c r="N52" s="3">
-        <v>5600</v>
+        <v>5700</v>
       </c>
       <c r="O52" s="3">
         <v>5600</v>
       </c>
       <c r="P52" s="3">
+        <v>5600</v>
+      </c>
+      <c r="Q52" s="3">
         <v>5100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>5300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>5700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>5600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>5400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>5000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>5500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>5800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>5300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>5700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3795,82 +3918,88 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>87900</v>
+      </c>
+      <c r="E54" s="3">
         <v>91600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>96200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>94000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>36200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>28500</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J54" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L54" s="3">
+      <c r="L54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M54" s="3">
         <v>149200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>129400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>128300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>126400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>131000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>112500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>109800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>98200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>97700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>93600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>96500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>96300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>89700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>91300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>89900</v>
       </c>
     </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3897,8 +4026,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3925,102 +4055,106 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E57" s="3">
         <v>900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1000</v>
-      </c>
-      <c r="F57" s="3">
-        <v>300</v>
       </c>
       <c r="G57" s="3">
         <v>300</v>
       </c>
       <c r="H57" s="3">
+        <v>300</v>
+      </c>
+      <c r="I57" s="3">
         <v>100</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J57" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L57" s="3">
+      <c r="L57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M57" s="3">
         <v>15200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>13900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>16100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>13500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>15400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>16000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>16600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>11400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>12000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>9400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>9000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>7700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>8100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>11400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>11700</v>
       </c>
     </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>62900</v>
+      </c>
+      <c r="E58" s="3">
         <v>48200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>49400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1800</v>
-      </c>
-      <c r="G58" s="3">
-        <v>500</v>
       </c>
       <c r="H58" s="3">
         <v>500</v>
       </c>
-      <c r="I58" s="3" t="s">
-        <v>8</v>
+      <c r="I58" s="3">
+        <v>500</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>8</v>
@@ -4028,35 +4162,35 @@
       <c r="K58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L58" s="3">
+      <c r="L58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M58" s="3">
         <v>8900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>7800</v>
-      </c>
-      <c r="N58" s="3">
-        <v>7600</v>
       </c>
       <c r="O58" s="3">
         <v>7600</v>
       </c>
       <c r="P58" s="3">
+        <v>7600</v>
+      </c>
+      <c r="Q58" s="3">
         <v>12400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>7300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>7000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>5200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>6200</v>
-      </c>
-      <c r="U58" s="3">
-        <v>6100</v>
       </c>
       <c r="V58" s="3">
         <v>6100</v>
@@ -4073,64 +4207,67 @@
       <c r="Z58" s="3">
         <v>6100</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3">
+        <v>6100</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E59" s="3">
         <v>20500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>30100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>16400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>12500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>5800</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J59" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M59" s="3">
         <v>3000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>500</v>
-      </c>
-      <c r="U59" s="3">
-        <v>300</v>
       </c>
       <c r="V59" s="3">
         <v>300</v>
@@ -4139,111 +4276,117 @@
         <v>300</v>
       </c>
       <c r="X59" s="3">
+        <v>300</v>
+      </c>
+      <c r="Y59" s="3">
         <v>1800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>69700</v>
+      </c>
+      <c r="E60" s="3">
         <v>69600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>80500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>18500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>13300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>6300</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J60" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L60" s="3">
+      <c r="L60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M60" s="3">
         <v>27000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>24300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>26900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>25000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>31700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>24500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>24000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>17200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>18800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>15700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>15400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>14100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>16000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>18400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>18200</v>
       </c>
     </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>300</v>
+      </c>
+      <c r="E61" s="3">
         <v>500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>59900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>18300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>18200</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -4251,72 +4394,75 @@
         <v>0</v>
       </c>
       <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
         <v>35800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>24400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>26400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>28400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>30400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>21900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>18700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>14400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>14900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>16200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>18900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>20400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>14700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>16200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>18300</v>
       </c>
     </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>200</v>
+      </c>
+      <c r="E62" s="3">
         <v>600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1000</v>
       </c>
-      <c r="H62" s="3">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>8</v>
+      <c r="I62" s="3">
+        <v>0</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>8</v>
@@ -4324,53 +4470,56 @@
       <c r="K62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M62" s="3">
         <v>18700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>14500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>11800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>10900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>7600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>6500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>6200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>5400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>5100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>5200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>8900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>8400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>8100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>8400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>7700</v>
       </c>
     </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4443,8 +4592,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4517,8 +4669,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4591,82 +4746,88 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>70100</v>
+      </c>
+      <c r="E66" s="3">
         <v>70700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>83500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>80600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>32800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>24500</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J66" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L66" s="3">
+      <c r="L66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M66" s="3">
         <v>81500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>63200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>65100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>64300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>69700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>52900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>48900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>37100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>38800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>37100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>43200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>42900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>38800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>43100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>44200</v>
       </c>
     </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4693,8 +4854,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4767,8 +4929,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4841,8 +5006,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4915,8 +5083,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4989,82 +5160,88 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>100</v>
+      </c>
+      <c r="E72" s="3">
         <v>3200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3200</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J72" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L72" s="3">
+      <c r="L72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M72" s="3">
         <v>49800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>48300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>45400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>44200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>43400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>41600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>41000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>41200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>39000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>36600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>33300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>33500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>31000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>28300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>25700</v>
       </c>
     </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5137,8 +5314,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5211,8 +5391,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5285,82 +5468,88 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>17800</v>
+      </c>
+      <c r="E76" s="3">
         <v>20900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>12700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>13400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3900</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J76" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L76" s="3">
+      <c r="L76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M76" s="3">
         <v>67700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>66200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>63200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>62000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>61200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>59600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>60900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>61100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>59000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>56500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>53300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>53400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>50900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>48300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>45700</v>
       </c>
     </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5433,161 +5622,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44834</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44651</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44469</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44286</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44104</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L80" s="2">
+      <c r="L80" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M80" s="2">
         <v>43921</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>43830</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>43738</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>43646</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>43555</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43465</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43373</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43281</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43190</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43100</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43008</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>42916</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>42825</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>42735</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E81" s="3">
         <v>4000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-2700</v>
       </c>
-      <c r="G81" s="3">
-        <v>0</v>
-      </c>
       <c r="H81" s="3">
+        <v>0</v>
+      </c>
+      <c r="I81" s="3">
         <v>600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>900</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L81" s="3">
+      <c r="L81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M81" s="3">
         <v>1500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>3300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>2600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5614,8 +5812,9 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5628,50 +5827,50 @@
       <c r="F83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G83" s="3">
+      <c r="G83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H83" s="3">
         <v>500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>100</v>
       </c>
-      <c r="J83" s="3">
-        <v>0</v>
-      </c>
-      <c r="K83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L83" s="3">
+      <c r="K83" s="3">
+        <v>0</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M83" s="3">
         <v>2900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2800</v>
-      </c>
-      <c r="N83" s="3">
-        <v>2700</v>
       </c>
       <c r="O83" s="3">
         <v>2700</v>
       </c>
       <c r="P83" s="3">
+        <v>2700</v>
+      </c>
+      <c r="Q83" s="3">
         <v>2600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>2400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>2100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>2000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1900</v>
-      </c>
-      <c r="U83" s="3">
-        <v>1800</v>
       </c>
       <c r="V83" s="3">
         <v>1800</v>
@@ -5680,16 +5879,19 @@
         <v>1800</v>
       </c>
       <c r="X83" s="3">
+        <v>1800</v>
+      </c>
+      <c r="Y83" s="3">
         <v>1700</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>1600</v>
       </c>
       <c r="Z83" s="3">
         <v>1600</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5762,8 +5964,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5836,8 +6041,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5910,8 +6118,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5984,8 +6195,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6058,82 +6272,88 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>6400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>4400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2200</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L89" s="3">
+      <c r="L89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M89" s="3">
         <v>-3900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>8000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>8800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>9100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>4200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-1100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>2900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>3800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>7700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>6000</v>
       </c>
     </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6160,8 +6380,9 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6190,52 +6411,55 @@
         <v>0</v>
       </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-5000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-12400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-7500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-4200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-3400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-2200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-12000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6308,8 +6532,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6382,82 +6609,88 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E94" s="3">
         <v>11600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>2500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-66000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-24300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-16300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-900</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L94" s="3">
+      <c r="L94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M94" s="3">
         <v>-4900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-12300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-4400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-6700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-4100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-2100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-6000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6484,8 +6717,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6558,8 +6792,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6632,8 +6869,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6706,8 +6946,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6780,93 +7023,99 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-9700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>66400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>17500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>13600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1200</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L100" s="3">
+      <c r="L100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M100" s="3">
         <v>12600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-6800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>13500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>6100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-2700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>5700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-2600</v>
       </c>
     </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-300</v>
+        <v>300</v>
       </c>
       <c r="E101" s="3">
         <v>-300</v>
       </c>
       <c r="F101" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="G101" s="3">
         <v>0</v>
@@ -6875,16 +7124,16 @@
         <v>0</v>
       </c>
       <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
         <v>100</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
-      <c r="K101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -6928,78 +7177,84 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>200</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L102" s="3">
+      <c r="L102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M102" s="3">
         <v>3700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>2700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>5100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>3700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-2200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>3600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-6700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-2000</v>
-      </c>
-      <c r="U102" s="3">
-        <v>-1900</v>
       </c>
       <c r="V102" s="3">
         <v>-1900</v>
       </c>
       <c r="W102" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="X102" s="3">
         <v>8100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-6400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>3800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GV_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GV_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="92">
   <si>
     <t>GV</t>
   </si>
@@ -663,13 +663,10 @@
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -703,22 +700,22 @@
         <v>45382</v>
       </c>
       <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
+        <v>45107</v>
+      </c>
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
+        <v>44926</v>
+      </c>
+      <c r="J7" s="2">
         <v>44834</v>
-      </c>
-      <c r="H7" s="2">
-        <v>44651</v>
-      </c>
-      <c r="I7" s="2">
-        <v>44469</v>
-      </c>
-      <c r="J7" s="2">
-        <v>44286</v>
       </c>
       <c r="K7" s="2">
         <v>44104</v>
@@ -777,25 +774,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>4400</v>
+        <v>2200</v>
       </c>
       <c r="E8" s="3">
-        <v>5000</v>
+        <v>2200</v>
       </c>
       <c r="F8" s="3">
-        <v>6600</v>
+        <v>2500</v>
       </c>
       <c r="G8" s="3">
-        <v>1900</v>
+        <v>2500</v>
       </c>
       <c r="H8" s="3">
-        <v>5200</v>
+        <v>3300</v>
       </c>
       <c r="I8" s="3">
-        <v>3200</v>
+        <v>3300</v>
       </c>
       <c r="J8" s="3">
-        <v>7700</v>
+        <v>900</v>
       </c>
       <c r="K8" s="3">
         <v>2000</v>
@@ -854,25 +851,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>3600</v>
+        <v>1800</v>
       </c>
       <c r="E9" s="3">
-        <v>3300</v>
+        <v>1800</v>
       </c>
       <c r="F9" s="3">
-        <v>3800</v>
+        <v>1600</v>
       </c>
       <c r="G9" s="3">
-        <v>800</v>
+        <v>1600</v>
       </c>
       <c r="H9" s="3">
-        <v>2600</v>
+        <v>1900</v>
       </c>
       <c r="I9" s="3">
-        <v>1500</v>
+        <v>1900</v>
       </c>
       <c r="J9" s="3">
-        <v>3500</v>
+        <v>400</v>
       </c>
       <c r="K9" s="3">
         <v>900</v>
@@ -931,25 +928,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>400</v>
+      </c>
+      <c r="E10" s="3">
+        <v>400</v>
+      </c>
+      <c r="F10" s="3">
         <v>800</v>
       </c>
-      <c r="E10" s="3">
-        <v>1700</v>
-      </c>
-      <c r="F10" s="3">
-        <v>2800</v>
-      </c>
       <c r="G10" s="3">
-        <v>1100</v>
+        <v>800</v>
       </c>
       <c r="H10" s="3">
-        <v>2600</v>
+        <v>1400</v>
       </c>
       <c r="I10" s="3">
-        <v>1700</v>
+        <v>1400</v>
       </c>
       <c r="J10" s="3">
-        <v>4200</v>
+        <v>500</v>
       </c>
       <c r="K10" s="3">
         <v>1100</v>
@@ -1191,25 +1188,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F14" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="G14" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="H14" s="3">
         <v>100</v>
       </c>
-      <c r="G14" s="3">
-        <v>-100</v>
-      </c>
-      <c r="H14" s="3">
-        <v>-100</v>
-      </c>
       <c r="I14" s="3">
-        <v>-400</v>
+        <v>100</v>
       </c>
       <c r="J14" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1268,25 +1265,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1371,25 +1368,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>4900</v>
+        <v>2400</v>
       </c>
       <c r="E17" s="3">
-        <v>6900</v>
+        <v>2400</v>
       </c>
       <c r="F17" s="3">
-        <v>5500</v>
+        <v>3400</v>
       </c>
       <c r="G17" s="3">
-        <v>2500</v>
+        <v>3400</v>
       </c>
       <c r="H17" s="3">
-        <v>4100</v>
+        <v>2700</v>
       </c>
       <c r="I17" s="3">
-        <v>1900</v>
+        <v>2700</v>
       </c>
       <c r="J17" s="3">
-        <v>3900</v>
+        <v>1300</v>
       </c>
       <c r="K17" s="3">
         <v>1000</v>
@@ -1448,25 +1445,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-500</v>
+        <v>-200</v>
       </c>
       <c r="E18" s="3">
-        <v>-1900</v>
+        <v>-200</v>
       </c>
       <c r="F18" s="3">
-        <v>1100</v>
+        <v>-1000</v>
       </c>
       <c r="G18" s="3">
-        <v>-600</v>
+        <v>-1000</v>
       </c>
       <c r="H18" s="3">
-        <v>1100</v>
+        <v>600</v>
       </c>
       <c r="I18" s="3">
-        <v>1300</v>
+        <v>600</v>
       </c>
       <c r="J18" s="3">
-        <v>3800</v>
+        <v>-400</v>
       </c>
       <c r="K18" s="3">
         <v>1000</v>
@@ -1557,22 +1554,22 @@
         <v>0</v>
       </c>
       <c r="E20" s="3">
-        <v>9700</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3">
-        <v>-400</v>
+        <v>-700</v>
       </c>
       <c r="G20" s="3">
-        <v>-1500</v>
+        <v>-700</v>
       </c>
       <c r="H20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I20" s="3">
         <v>0</v>
       </c>
       <c r="J20" s="3">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="K20" s="3">
         <v>300</v>
@@ -1630,26 +1627,26 @@
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>8</v>
+      <c r="D21" s="3">
+        <v>400</v>
+      </c>
+      <c r="E21" s="3">
+        <v>200</v>
+      </c>
+      <c r="F21" s="3">
+        <v>100</v>
+      </c>
+      <c r="G21" s="3">
+        <v>100</v>
       </c>
       <c r="H21" s="3">
-        <v>1700</v>
+        <v>900</v>
       </c>
       <c r="I21" s="3">
-        <v>1500</v>
+        <v>700</v>
       </c>
       <c r="J21" s="3">
-        <v>4100</v>
+        <v>-1000</v>
       </c>
       <c r="K21" s="3">
         <v>1300</v>
@@ -1708,25 +1705,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="E22" s="3">
-        <v>2800</v>
+        <v>1500</v>
       </c>
       <c r="F22" s="3">
-        <v>2400</v>
+        <v>1600</v>
       </c>
       <c r="G22" s="3">
-        <v>500</v>
+        <v>1600</v>
       </c>
       <c r="H22" s="3">
-        <v>900</v>
+        <v>1400</v>
       </c>
       <c r="I22" s="3">
-        <v>400</v>
+        <v>1400</v>
       </c>
       <c r="J22" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1785,25 +1782,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-3500</v>
+        <v>-1800</v>
       </c>
       <c r="E23" s="3">
-        <v>5000</v>
+        <v>-1800</v>
       </c>
       <c r="F23" s="3">
-        <v>-1800</v>
+        <v>2500</v>
       </c>
       <c r="G23" s="3">
-        <v>-2700</v>
+        <v>2500</v>
       </c>
       <c r="H23" s="3">
-        <v>300</v>
+        <v>-900</v>
       </c>
       <c r="I23" s="3">
-        <v>900</v>
+        <v>-900</v>
       </c>
       <c r="J23" s="3">
-        <v>3900</v>
+        <v>-1300</v>
       </c>
       <c r="K23" s="3">
         <v>1200</v>
@@ -1862,25 +1859,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E24" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F24" s="3">
+        <v>500</v>
+      </c>
+      <c r="G24" s="3">
+        <v>500</v>
+      </c>
+      <c r="H24" s="3">
         <v>-500</v>
       </c>
-      <c r="E24" s="3">
-        <v>1100</v>
-      </c>
-      <c r="F24" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="G24" s="3">
-        <v>100</v>
-      </c>
-      <c r="H24" s="3">
-        <v>300</v>
-      </c>
       <c r="I24" s="3">
-        <v>300</v>
+        <v>-500</v>
       </c>
       <c r="J24" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="K24" s="3">
         <v>300</v>
@@ -2016,25 +2013,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-3000</v>
+        <v>-1500</v>
       </c>
       <c r="E26" s="3">
-        <v>4000</v>
+        <v>-1500</v>
       </c>
       <c r="F26" s="3">
-        <v>-800</v>
+        <v>2000</v>
       </c>
       <c r="G26" s="3">
-        <v>-2800</v>
+        <v>2000</v>
       </c>
       <c r="H26" s="3">
-        <v>-100</v>
+        <v>-400</v>
       </c>
       <c r="I26" s="3">
-        <v>600</v>
+        <v>-400</v>
       </c>
       <c r="J26" s="3">
-        <v>2900</v>
+        <v>-1400</v>
       </c>
       <c r="K26" s="3">
         <v>900</v>
@@ -2093,25 +2090,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-3000</v>
+        <v>-1500</v>
       </c>
       <c r="E27" s="3">
-        <v>4000</v>
+        <v>-1500</v>
       </c>
       <c r="F27" s="3">
-        <v>-800</v>
+        <v>2000</v>
       </c>
       <c r="G27" s="3">
-        <v>-2700</v>
+        <v>2000</v>
       </c>
       <c r="H27" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="I27" s="3">
-        <v>600</v>
+        <v>-400</v>
       </c>
       <c r="J27" s="3">
-        <v>2900</v>
+        <v>-1400</v>
       </c>
       <c r="K27" s="3">
         <v>900</v>
@@ -2481,22 +2478,22 @@
         <v>0</v>
       </c>
       <c r="E32" s="3">
-        <v>-9700</v>
+        <v>0</v>
       </c>
       <c r="F32" s="3">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="G32" s="3">
-        <v>1500</v>
+        <v>700</v>
       </c>
       <c r="H32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I32" s="3">
         <v>0</v>
       </c>
       <c r="J32" s="3">
-        <v>-300</v>
+        <v>-800</v>
       </c>
       <c r="K32" s="3">
         <v>-300</v>
@@ -2555,25 +2552,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-3000</v>
+        <v>-1500</v>
       </c>
       <c r="E33" s="3">
-        <v>4000</v>
+        <v>-1500</v>
       </c>
       <c r="F33" s="3">
-        <v>-800</v>
+        <v>2000</v>
       </c>
       <c r="G33" s="3">
-        <v>-2700</v>
+        <v>2000</v>
       </c>
       <c r="H33" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="I33" s="3">
-        <v>600</v>
+        <v>-400</v>
       </c>
       <c r="J33" s="3">
-        <v>2900</v>
+        <v>-1400</v>
       </c>
       <c r="K33" s="3">
         <v>900</v>
@@ -2709,25 +2706,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-3000</v>
+        <v>-1500</v>
       </c>
       <c r="E35" s="3">
-        <v>4000</v>
+        <v>-1500</v>
       </c>
       <c r="F35" s="3">
-        <v>-800</v>
+        <v>2000</v>
       </c>
       <c r="G35" s="3">
-        <v>-2700</v>
+        <v>2000</v>
       </c>
       <c r="H35" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="I35" s="3">
-        <v>600</v>
+        <v>-400</v>
       </c>
       <c r="J35" s="3">
-        <v>2900</v>
+        <v>-1400</v>
       </c>
       <c r="K35" s="3">
         <v>900</v>
@@ -2794,22 +2791,22 @@
         <v>45382</v>
       </c>
       <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
+        <v>45107</v>
+      </c>
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
+        <v>44926</v>
+      </c>
+      <c r="J38" s="2">
         <v>44834</v>
-      </c>
-      <c r="H38" s="2">
-        <v>44651</v>
-      </c>
-      <c r="I38" s="2">
-        <v>44469</v>
-      </c>
-      <c r="J38" s="2">
-        <v>44286</v>
       </c>
       <c r="K38" s="2">
         <v>44104</v>
@@ -2929,22 +2926,22 @@
         <v>600</v>
       </c>
       <c r="E41" s="3">
+        <v>600</v>
+      </c>
+      <c r="F41" s="3">
         <v>400</v>
       </c>
-      <c r="F41" s="3">
-        <v>700</v>
-      </c>
       <c r="G41" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="H41" s="3">
         <v>700</v>
       </c>
       <c r="I41" s="3">
-        <v>300</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>8</v>
+        <v>700</v>
+      </c>
+      <c r="J41" s="3">
+        <v>200</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>8</v>
@@ -3006,22 +3003,22 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
-        <v>100</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>8</v>
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>8</v>
@@ -3083,7 +3080,7 @@
         <v>100</v>
       </c>
       <c r="E43" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F43" s="3">
         <v>300</v>
@@ -3092,13 +3089,13 @@
         <v>300</v>
       </c>
       <c r="H43" s="3">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="I43" s="3">
-        <v>1400</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>8</v>
+        <v>300</v>
+      </c>
+      <c r="J43" s="3">
+        <v>300</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>8</v>
@@ -3168,11 +3165,11 @@
       <c r="G44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>200</v>
+      <c r="H44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>8</v>
@@ -3237,22 +3234,22 @@
         <v>1400</v>
       </c>
       <c r="E45" s="3">
-        <v>17600</v>
+        <v>1400</v>
       </c>
       <c r="F45" s="3">
-        <v>21400</v>
+        <v>17100</v>
       </c>
       <c r="G45" s="3">
+        <v>17100</v>
+      </c>
+      <c r="H45" s="3">
+        <v>20900</v>
+      </c>
+      <c r="I45" s="3">
+        <v>20900</v>
+      </c>
+      <c r="J45" s="3">
         <v>300</v>
-      </c>
-      <c r="H45" s="3">
-        <v>200</v>
-      </c>
-      <c r="I45" s="3">
-        <v>300</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>8</v>
@@ -3314,22 +3311,22 @@
         <v>2100</v>
       </c>
       <c r="E46" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F46" s="3">
         <v>18300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
+        <v>18300</v>
+      </c>
+      <c r="H46" s="3">
         <v>22300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
+        <v>22300</v>
+      </c>
+      <c r="J46" s="3">
         <v>900</v>
-      </c>
-      <c r="H46" s="3">
-        <v>1500</v>
-      </c>
-      <c r="I46" s="3">
-        <v>2300</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>8</v>
@@ -3387,26 +3384,26 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>2400</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F47" s="3">
-        <v>800</v>
+        <v>100</v>
       </c>
       <c r="G47" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="H47" s="3">
-        <v>7400</v>
+        <v>100</v>
       </c>
       <c r="I47" s="3">
-        <v>2500</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>8</v>
+        <v>100</v>
+      </c>
+      <c r="J47" s="3">
+        <v>100</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>8</v>
@@ -3468,22 +3465,22 @@
         <v>83600</v>
       </c>
       <c r="E48" s="3">
+        <v>83600</v>
+      </c>
+      <c r="F48" s="3">
         <v>68700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
+        <v>68700</v>
+      </c>
+      <c r="H48" s="3">
         <v>70300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
+        <v>70300</v>
+      </c>
+      <c r="J48" s="3">
         <v>90100</v>
-      </c>
-      <c r="H48" s="3">
-        <v>24200</v>
-      </c>
-      <c r="I48" s="3">
-        <v>23000</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>8</v>
@@ -3554,13 +3551,13 @@
         <v>1900</v>
       </c>
       <c r="H49" s="3">
-        <v>2100</v>
+        <v>1900</v>
       </c>
       <c r="I49" s="3">
-        <v>700</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>8</v>
+        <v>1900</v>
+      </c>
+      <c r="J49" s="3">
+        <v>1900</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>8</v>
@@ -3773,25 +3770,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E52" s="3">
         <v>200</v>
       </c>
       <c r="F52" s="3">
+        <v>2600</v>
+      </c>
+      <c r="G52" s="3">
+        <v>2600</v>
+      </c>
+      <c r="H52" s="3">
         <v>900</v>
       </c>
-      <c r="G52" s="3">
-        <v>600</v>
-      </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
+        <v>900</v>
+      </c>
+      <c r="J52" s="3">
         <v>1000</v>
-      </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>8</v>
@@ -3930,22 +3927,22 @@
         <v>87900</v>
       </c>
       <c r="E54" s="3">
+        <v>87900</v>
+      </c>
+      <c r="F54" s="3">
         <v>91600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
+        <v>91600</v>
+      </c>
+      <c r="H54" s="3">
         <v>96200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
+        <v>96200</v>
+      </c>
+      <c r="J54" s="3">
         <v>94000</v>
-      </c>
-      <c r="H54" s="3">
-        <v>36200</v>
-      </c>
-      <c r="I54" s="3">
-        <v>28500</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>8</v>
@@ -4065,22 +4062,22 @@
         <v>1200</v>
       </c>
       <c r="E57" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F57" s="3">
         <v>900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
+        <v>900</v>
+      </c>
+      <c r="H57" s="3">
         <v>1000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J57" s="3">
         <v>300</v>
-      </c>
-      <c r="H57" s="3">
-        <v>300</v>
-      </c>
-      <c r="I57" s="3">
-        <v>100</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>8</v>
@@ -4139,25 +4136,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>62900</v>
+        <v>63200</v>
       </c>
       <c r="E58" s="3">
-        <v>48200</v>
+        <v>63200</v>
       </c>
       <c r="F58" s="3">
-        <v>49400</v>
+        <v>48500</v>
       </c>
       <c r="G58" s="3">
-        <v>1800</v>
+        <v>48500</v>
       </c>
       <c r="H58" s="3">
-        <v>500</v>
+        <v>53700</v>
       </c>
       <c r="I58" s="3">
-        <v>500</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>8</v>
+        <v>53700</v>
+      </c>
+      <c r="J58" s="3">
+        <v>12500</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>8</v>
@@ -4216,25 +4213,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>5600</v>
+        <v>2400</v>
       </c>
       <c r="E59" s="3">
-        <v>20500</v>
+        <v>2400</v>
       </c>
       <c r="F59" s="3">
-        <v>30100</v>
+        <v>17000</v>
       </c>
       <c r="G59" s="3">
-        <v>16400</v>
+        <v>17000</v>
       </c>
       <c r="H59" s="3">
-        <v>12500</v>
+        <v>22900</v>
       </c>
       <c r="I59" s="3">
-        <v>5800</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>8</v>
+        <v>22900</v>
+      </c>
+      <c r="J59" s="3">
+        <v>2500</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>8</v>
@@ -4296,22 +4293,22 @@
         <v>69700</v>
       </c>
       <c r="E60" s="3">
+        <v>69700</v>
+      </c>
+      <c r="F60" s="3">
         <v>69600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
+        <v>69600</v>
+      </c>
+      <c r="H60" s="3">
         <v>80500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
+        <v>80500</v>
+      </c>
+      <c r="J60" s="3">
         <v>18500</v>
-      </c>
-      <c r="H60" s="3">
-        <v>13300</v>
-      </c>
-      <c r="I60" s="3">
-        <v>6300</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>8</v>
@@ -4373,22 +4370,22 @@
         <v>300</v>
       </c>
       <c r="E61" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="F61" s="3">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="G61" s="3">
-        <v>59900</v>
+        <v>900</v>
       </c>
       <c r="H61" s="3">
-        <v>18300</v>
+        <v>1200</v>
       </c>
       <c r="I61" s="3">
-        <v>18200</v>
+        <v>1200</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>60500</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -4447,25 +4444,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E62" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="F62" s="3">
-        <v>2300</v>
+        <v>0</v>
       </c>
       <c r="G62" s="3">
-        <v>2100</v>
+        <v>0</v>
       </c>
       <c r="H62" s="3">
-        <v>1000</v>
+        <v>1600</v>
       </c>
       <c r="I62" s="3">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>8</v>
+        <v>1600</v>
+      </c>
+      <c r="J62" s="3">
+        <v>1300</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>8</v>
@@ -4758,22 +4755,22 @@
         <v>70100</v>
       </c>
       <c r="E66" s="3">
+        <v>70100</v>
+      </c>
+      <c r="F66" s="3">
         <v>70700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
+        <v>70700</v>
+      </c>
+      <c r="H66" s="3">
         <v>83500</v>
       </c>
-      <c r="G66" s="3">
-        <v>80600</v>
-      </c>
-      <c r="H66" s="3">
-        <v>32800</v>
-      </c>
       <c r="I66" s="3">
-        <v>24500</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>8</v>
+        <v>83500</v>
+      </c>
+      <c r="J66" s="3">
+        <v>80500</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>8</v>
@@ -5172,22 +5169,22 @@
         <v>100</v>
       </c>
       <c r="E72" s="3">
+        <v>100</v>
+      </c>
+      <c r="F72" s="3">
         <v>3200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
+        <v>3200</v>
+      </c>
+      <c r="H72" s="3">
         <v>-900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
+        <v>-900</v>
+      </c>
+      <c r="J72" s="3">
         <v>-100</v>
-      </c>
-      <c r="H72" s="3">
-        <v>2600</v>
-      </c>
-      <c r="I72" s="3">
-        <v>3200</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>8</v>
@@ -5480,22 +5477,22 @@
         <v>17800</v>
       </c>
       <c r="E76" s="3">
+        <v>17800</v>
+      </c>
+      <c r="F76" s="3">
         <v>20900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
+        <v>20900</v>
+      </c>
+      <c r="H76" s="3">
         <v>12700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
+        <v>12700</v>
+      </c>
+      <c r="J76" s="3">
         <v>13400</v>
-      </c>
-      <c r="H76" s="3">
-        <v>3400</v>
-      </c>
-      <c r="I76" s="3">
-        <v>3900</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>8</v>
@@ -5639,22 +5636,22 @@
         <v>45382</v>
       </c>
       <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
+        <v>45107</v>
+      </c>
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
+        <v>44926</v>
+      </c>
+      <c r="J80" s="2">
         <v>44834</v>
-      </c>
-      <c r="H80" s="2">
-        <v>44651</v>
-      </c>
-      <c r="I80" s="2">
-        <v>44469</v>
-      </c>
-      <c r="J80" s="2">
-        <v>44286</v>
       </c>
       <c r="K80" s="2">
         <v>44104</v>
@@ -5713,25 +5710,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-3000</v>
+        <v>-1500</v>
       </c>
       <c r="E81" s="3">
-        <v>4000</v>
+        <v>-1500</v>
       </c>
       <c r="F81" s="3">
-        <v>-800</v>
+        <v>2000</v>
       </c>
       <c r="G81" s="3">
-        <v>-2700</v>
+        <v>2000</v>
       </c>
       <c r="H81" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="I81" s="3">
-        <v>600</v>
+        <v>-400</v>
       </c>
       <c r="J81" s="3">
-        <v>2900</v>
+        <v>-1400</v>
       </c>
       <c r="K81" s="3">
         <v>900</v>
@@ -5831,10 +5828,10 @@
         <v>8</v>
       </c>
       <c r="H83" s="3">
-        <v>500</v>
-      </c>
-      <c r="I83" s="3">
-        <v>200</v>
+        <v>100</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J83" s="3">
         <v>100</v>
@@ -6280,26 +6277,26 @@
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="E89" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="F89" s="3">
-        <v>700</v>
-      </c>
-      <c r="G89" s="3">
-        <v>-400</v>
-      </c>
-      <c r="H89" s="3">
-        <v>6400</v>
-      </c>
-      <c r="I89" s="3">
-        <v>1800</v>
-      </c>
-      <c r="J89" s="3">
-        <v>4400</v>
+      <c r="D89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K89" s="3">
         <v>2200</v>
@@ -6386,26 +6383,26 @@
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>-16600</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-17100</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-200</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -6617,26 +6614,26 @@
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>1500</v>
-      </c>
-      <c r="E94" s="3">
-        <v>11600</v>
-      </c>
-      <c r="F94" s="3">
-        <v>2500</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-66000</v>
-      </c>
-      <c r="H94" s="3">
-        <v>-24300</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-16300</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-3100</v>
+      <c r="D94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K94" s="3">
         <v>-900</v>
@@ -6723,26 +6720,26 @@
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -7031,26 +7028,26 @@
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>300</v>
-      </c>
-      <c r="E100" s="3">
-        <v>-9700</v>
-      </c>
-      <c r="F100" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="G100" s="3">
-        <v>66400</v>
-      </c>
-      <c r="H100" s="3">
-        <v>17500</v>
-      </c>
-      <c r="I100" s="3">
-        <v>13600</v>
-      </c>
-      <c r="J100" s="3">
-        <v>-400</v>
+      <c r="D100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K100" s="3">
         <v>-1200</v>
@@ -7108,26 +7105,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>300</v>
-      </c>
-      <c r="E101" s="3">
-        <v>-300</v>
-      </c>
-      <c r="F101" s="3">
-        <v>-300</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H101" s="3">
         <v>0</v>
       </c>
-      <c r="I101" s="3">
-        <v>0</v>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J101" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -7186,25 +7183,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="E102" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="F102" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="G102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H102" s="3">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="I102" s="3">
-        <v>-900</v>
+        <v>0</v>
       </c>
       <c r="J102" s="3">
-        <v>1100</v>
+        <v>0</v>
       </c>
       <c r="K102" s="3">
         <v>200</v>

--- a/AAII_Financials/Quarterly/GV_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GV_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="92">
   <si>
     <t>GV</t>
   </si>
@@ -656,274 +656,294 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44104</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O7" s="2">
         <v>43921</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>43830</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>43738</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>43646</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43555</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43465</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43373</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43281</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43190</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43100</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43008</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>42916</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>42825</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>42735</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F8" s="3">
         <v>2200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>2200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>2500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>2500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>3300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>3300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>2000</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O8" s="3">
         <v>44800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>44100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>44700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>44400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>47500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>36700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>29500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>37500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>34400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>29600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>24500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>29100</v>
-      </c>
-      <c r="Y8" s="3">
-        <v>30700</v>
-      </c>
-      <c r="Z8" s="3">
-        <v>31800</v>
       </c>
       <c r="AA8" s="3">
         <v>30700</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3">
+        <v>31800</v>
+      </c>
+      <c r="AC8" s="3">
+        <v>30700</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F9" s="3">
         <v>1800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>1800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>1600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>1600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>1900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>1900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>900</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O9" s="3">
         <v>37700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>34200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>37800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>37700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>39500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>31800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>26100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>30100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>27000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>24500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>20900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>21600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>22900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>24400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>23800</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -934,73 +954,79 @@
         <v>400</v>
       </c>
       <c r="F10" s="3">
+        <v>400</v>
+      </c>
+      <c r="G10" s="3">
+        <v>400</v>
+      </c>
+      <c r="H10" s="3">
         <v>800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>1400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>1400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>1100</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O10" s="3">
         <v>7100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>9900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>6900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>6700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>8000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>4900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>3400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>7400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>7400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>5100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>3600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>7500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>7800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>7400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1028,8 +1054,10 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1105,8 +1133,14 @@
       <c r="AA12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1182,43 +1216,49 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3">
         <v>100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>-4400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>-4400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>100</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
+      <c r="L14" s="3">
+        <v>0</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
@@ -1259,8 +1299,14 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1268,10 +1314,10 @@
         <v>600</v>
       </c>
       <c r="E15" s="3">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="F15" s="3">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="G15" s="3">
         <v>300</v>
@@ -1280,64 +1326,70 @@
         <v>300</v>
       </c>
       <c r="I15" s="3">
+        <v>300</v>
+      </c>
+      <c r="J15" s="3">
+        <v>300</v>
+      </c>
+      <c r="K15" s="3">
         <v>100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>100</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3">
         <v>2900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>2800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>2700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>2700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>2600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>2400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>2100</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>2000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>1900</v>
-      </c>
-      <c r="V15" s="3">
-        <v>1800</v>
-      </c>
-      <c r="W15" s="3">
-        <v>1800</v>
       </c>
       <c r="X15" s="3">
         <v>1800</v>
       </c>
       <c r="Y15" s="3">
+        <v>1800</v>
+      </c>
+      <c r="Z15" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AA15" s="3">
         <v>1700</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AB15" s="3">
         <v>1600</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AC15" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1362,162 +1414,176 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F17" s="3">
         <v>2400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>2400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>3400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>3400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>2700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>2700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>1300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>1000</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O17" s="3">
         <v>43200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>39500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>42700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>42700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>44600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>35800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>29600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>34100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>31000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>28000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>24400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>25000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>26400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>27300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>26900</v>
       </c>
     </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F18" s="3">
         <v>-200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-1000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-1000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>1000</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O18" s="3">
         <v>1600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>4600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>2000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>1700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>2900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>3400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>3400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>1600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>4100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>4300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>4500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1545,43 +1611,45 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>-700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-700</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>300</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M20" s="3">
-        <v>100</v>
-      </c>
-      <c r="N20" s="3">
-        <v>0</v>
+      <c r="N20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O20" s="3">
         <v>100</v>
@@ -1590,13 +1658,13 @@
         <v>0</v>
       </c>
       <c r="Q20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
       <c r="S20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T20" s="3">
         <v>0</v>
@@ -1608,7 +1676,7 @@
         <v>0</v>
       </c>
       <c r="W20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X20" s="3">
         <v>0</v>
@@ -1622,138 +1690,150 @@
       <c r="AA20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="F21" s="3">
         <v>400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-1000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>1300</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O21" s="3">
         <v>4600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>7400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>4900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>4500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>5500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>3300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>2100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>5400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>5400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>3500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>2000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>5900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>6100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>6100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E22" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F22" s="3">
         <v>1500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>1500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>1600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>1600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>1400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>1400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>300</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O22" s="3">
         <v>300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>300</v>
-      </c>
-      <c r="O22" s="3">
-        <v>400</v>
-      </c>
-      <c r="P22" s="3">
-        <v>400</v>
       </c>
       <c r="Q22" s="3">
         <v>400</v>
       </c>
       <c r="R22" s="3">
+        <v>400</v>
+      </c>
+      <c r="S22" s="3">
+        <v>400</v>
+      </c>
+      <c r="T22" s="3">
         <v>300</v>
-      </c>
-      <c r="S22" s="3">
-        <v>200</v>
-      </c>
-      <c r="T22" s="3">
-        <v>200</v>
       </c>
       <c r="U22" s="3">
         <v>200</v>
@@ -1765,10 +1845,10 @@
         <v>200</v>
       </c>
       <c r="X22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Y22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Z22" s="3">
         <v>100</v>
@@ -1776,162 +1856,180 @@
       <c r="AA22" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC22" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="F23" s="3">
         <v>-1800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-1800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>2500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>2500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-1300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>1200</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O23" s="3">
         <v>1400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>4300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>1800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>1300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>2600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>3200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>3300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>1500</v>
       </c>
-      <c r="W23" s="3">
-        <v>0</v>
-      </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="3">
         <v>4000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>4200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>4300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>100</v>
+      </c>
+      <c r="E24" s="3">
+        <v>100</v>
+      </c>
+      <c r="F24" s="3">
         <v>-300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>-300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>-500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>-500</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>300</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O24" s="3">
         <v>-100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>1400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>800</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
         <v>-100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>1000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>500</v>
       </c>
-      <c r="W24" s="3">
-        <v>0</v>
-      </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3">
         <v>1500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>1500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>1700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2007,162 +2105,180 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="F26" s="3">
         <v>-1500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-1500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>2000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>2000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-1400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>900</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O26" s="3">
         <v>1500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>3000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>1200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>1800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>2200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>2400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>2500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>2700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>2600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="F27" s="3">
         <v>-1500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-1500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>2000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>2000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-1400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>900</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O27" s="3">
         <v>1500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>3000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>1200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>1800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>2200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>2400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>2500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>2700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>2600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2238,8 +2354,14 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2270,11 +2392,11 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N29" s="3" t="s">
-        <v>8</v>
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
+        <v>0</v>
       </c>
       <c r="O29" s="3" t="s">
         <v>8</v>
@@ -2285,38 +2407,44 @@
       <c r="Q29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R29" s="3">
-        <v>0</v>
-      </c>
-      <c r="S29" s="3">
-        <v>0</v>
-      </c>
-      <c r="T29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V29" s="3">
+      <c r="R29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X29" s="3">
         <v>2300</v>
       </c>
-      <c r="W29" s="3">
+      <c r="Y29" s="3">
         <v>-100</v>
       </c>
-      <c r="X29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y29" s="3">
-        <v>0</v>
-      </c>
       <c r="Z29" s="3">
         <v>0</v>
       </c>
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2392,8 +2520,14 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2469,43 +2603,49 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>-1600</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>-1600</v>
       </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>700</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-300</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="N32" s="3">
-        <v>0</v>
+      <c r="N32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O32" s="3">
         <v>-100</v>
@@ -2514,13 +2654,13 @@
         <v>0</v>
       </c>
       <c r="Q32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
       <c r="S32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="T32" s="3">
         <v>0</v>
@@ -2532,7 +2672,7 @@
         <v>0</v>
       </c>
       <c r="W32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="X32" s="3">
         <v>0</v>
@@ -2546,85 +2686,97 @@
       <c r="AA32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="F33" s="3">
         <v>-1500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-1500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>2000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>2000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-1400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>900</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O33" s="3">
         <v>1500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>3000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>1200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>1800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>2200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>2400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>3300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>2500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>2700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>2600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2700,167 +2852,185 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="F35" s="3">
         <v>-1500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-1500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>2000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>2000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-1400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>900</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O35" s="3">
         <v>1500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>3000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>1200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>1800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>2200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>2400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>3300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>2500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>2700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>2600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44104</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O38" s="2">
         <v>43921</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>43830</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>43738</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>43646</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43555</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43465</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43373</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43281</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43190</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43100</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43008</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>42916</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>42825</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>42735</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2888,8 +3058,10 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2917,85 +3089,93 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>200</v>
+      </c>
+      <c r="E41" s="3">
+        <v>200</v>
+      </c>
+      <c r="F41" s="3">
         <v>600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>200</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M41" s="3">
+      <c r="M41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O41" s="3">
         <v>27000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>23300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>20600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>15500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>15000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>11400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>13600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>9900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>16600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>18500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>20400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>22400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>14200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>20600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>16800</v>
       </c>
     </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3020,17 +3200,17 @@
       <c r="J42" s="3">
         <v>0</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
-      <c r="N42" s="3">
-        <v>0</v>
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O42" s="3">
         <v>0</v>
@@ -3071,22 +3251,28 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>0</v>
+      </c>
+      <c r="E43" s="3">
+        <v>0</v>
+      </c>
+      <c r="F43" s="3">
         <v>100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>100</v>
-      </c>
-      <c r="F43" s="3">
-        <v>300</v>
-      </c>
-      <c r="G43" s="3">
-        <v>300</v>
       </c>
       <c r="H43" s="3">
         <v>300</v>
@@ -3097,59 +3283,65 @@
       <c r="J43" s="3">
         <v>300</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M43" s="3">
+      <c r="K43" s="3">
+        <v>300</v>
+      </c>
+      <c r="L43" s="3">
+        <v>300</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O43" s="3">
         <v>44000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>34700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>37800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>39200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>42400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>35500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>33400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>34800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>30200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>22200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>20000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>19300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>17000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>19600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>19200</v>
       </c>
     </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3180,207 +3372,225 @@
       <c r="L44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M44" s="3">
+      <c r="M44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O44" s="3">
         <v>1000</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P44" s="3">
+      <c r="P44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R44" s="3">
         <v>1000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>5100</v>
       </c>
-      <c r="R44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T44" s="3" t="s">
         <v>8</v>
       </c>
       <c r="U44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V44" s="3">
+      <c r="V44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X44" s="3">
         <v>6100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>7300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>6400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>10400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>7300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>12000</v>
       </c>
     </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E45" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F45" s="3">
         <v>1400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>1400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>17100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>17100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>20900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>20900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>300</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O45" s="3">
         <v>2200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>3000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>2700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>2700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>2600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>10700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>9000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>6800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>6300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>4900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>5200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>4300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>4600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>3900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F46" s="3">
         <v>2100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>2100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>18300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>18300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>22300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>22300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>900</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M46" s="3">
+      <c r="M46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O46" s="3">
         <v>74200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>61000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>61200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>58400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>65300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>57600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>55900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>51500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>53100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>51700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>52900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>52400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>46200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>51400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>52800</v>
       </c>
     </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3390,11 +3600,11 @@
       <c r="E47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F47" s="3">
-        <v>100</v>
-      </c>
-      <c r="G47" s="3">
-        <v>100</v>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H47" s="3">
         <v>100</v>
@@ -3405,17 +3615,17 @@
       <c r="J47" s="3">
         <v>100</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
-      <c r="N47" s="3">
-        <v>0</v>
+      <c r="K47" s="3">
+        <v>100</v>
+      </c>
+      <c r="L47" s="3">
+        <v>100</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O47" s="3">
         <v>0</v>
@@ -3456,85 +3666,97 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>82800</v>
+      </c>
+      <c r="E48" s="3">
+        <v>82800</v>
+      </c>
+      <c r="F48" s="3">
         <v>83600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>83600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>68700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>68700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>70300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>70300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>90100</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M48" s="3">
+      <c r="M48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O48" s="3">
         <v>68600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>61900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>60900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>61600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>59800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>48900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>47500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>40200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>38400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>36100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>37200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>37300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>37400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>33200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>32800</v>
       </c>
     </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3559,26 +3781,26 @@
       <c r="J49" s="3">
         <v>1900</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M49" s="3">
-        <v>700</v>
-      </c>
-      <c r="N49" s="3">
-        <v>700</v>
+      <c r="K49" s="3">
+        <v>1900</v>
+      </c>
+      <c r="L49" s="3">
+        <v>1900</v>
+      </c>
+      <c r="M49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O49" s="3">
         <v>700</v>
       </c>
       <c r="P49" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="Q49" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="R49" s="3">
         <v>800</v>
@@ -3593,10 +3815,10 @@
         <v>800</v>
       </c>
       <c r="V49" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="W49" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="X49" s="3">
         <v>900</v>
@@ -3610,8 +3832,14 @@
       <c r="AA49" s="3">
         <v>900</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3">
+        <v>900</v>
+      </c>
+      <c r="AC49" s="3">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3687,8 +3915,14 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3764,8 +3998,14 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3776,73 +4016,79 @@
         <v>200</v>
       </c>
       <c r="F52" s="3">
+        <v>200</v>
+      </c>
+      <c r="G52" s="3">
+        <v>200</v>
+      </c>
+      <c r="H52" s="3">
         <v>2600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>2600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>1000</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M52" s="3">
+      <c r="M52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O52" s="3">
         <v>5700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>5700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>5600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>5600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>5100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>5300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>5700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>5600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>5400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>5000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>5500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>5800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>5300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>5700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3918,85 +4164,97 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>86600</v>
+      </c>
+      <c r="E54" s="3">
+        <v>86600</v>
+      </c>
+      <c r="F54" s="3">
         <v>87900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>87900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>91600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>91600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>96200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>96200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>94000</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M54" s="3">
+      <c r="M54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O54" s="3">
         <v>149200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>129400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>128300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>126400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>131000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>112500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>109800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>98200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>97700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>93600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>96500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>96300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>89700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>91300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>89900</v>
       </c>
     </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4024,8 +4282,10 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4053,147 +4313,155 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>800</v>
+      </c>
+      <c r="E57" s="3">
+        <v>800</v>
+      </c>
+      <c r="F57" s="3">
         <v>1200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>1000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>1000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>300</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M57" s="3">
+      <c r="M57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O57" s="3">
         <v>15200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>13900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>16100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>13500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>15400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>16000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>16600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>11400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>12000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>9400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>9000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>7700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>8100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>11400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>11700</v>
       </c>
     </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>64300</v>
+      </c>
+      <c r="E58" s="3">
+        <v>64300</v>
+      </c>
+      <c r="F58" s="3">
         <v>63200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>63200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>48500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>48500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>53700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>53700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>12500</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M58" s="3">
+      <c r="M58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O58" s="3">
         <v>8900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>7800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>7600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>7600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>12400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>7300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>7000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>5200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>6200</v>
-      </c>
-      <c r="V58" s="3">
-        <v>6100</v>
-      </c>
-      <c r="W58" s="3">
-        <v>6100</v>
       </c>
       <c r="X58" s="3">
         <v>6100</v>
@@ -4207,247 +4475,271 @@
       <c r="AA58" s="3">
         <v>6100</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3">
+        <v>6100</v>
+      </c>
+      <c r="AC58" s="3">
+        <v>6100</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F59" s="3">
         <v>2400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>2400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>17000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>17000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>22900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>22900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>2500</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O59" s="3">
         <v>3000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>2700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>3200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>4000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>3900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>1200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>500</v>
-      </c>
-      <c r="V59" s="3">
-        <v>300</v>
-      </c>
-      <c r="W59" s="3">
-        <v>300</v>
       </c>
       <c r="X59" s="3">
         <v>300</v>
       </c>
       <c r="Y59" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z59" s="3">
+        <v>300</v>
+      </c>
+      <c r="AA59" s="3">
         <v>1800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>70600</v>
+      </c>
+      <c r="E60" s="3">
+        <v>70600</v>
+      </c>
+      <c r="F60" s="3">
         <v>69700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>69700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>69600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>69600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>80500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>80500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>18500</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M60" s="3">
+      <c r="M60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O60" s="3">
         <v>27000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>24300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>26900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>25000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>31700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>24500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>24000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>17200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>18800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>15700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>15400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>14100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>16000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>18400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>18200</v>
       </c>
     </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
         <v>300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>1200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>1200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>60500</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
         <v>35800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>24400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>26400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>28400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>30400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>21900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>18700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>14400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>14900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>16200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>18900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>20400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>14700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>16200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>18300</v>
       </c>
     </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="F62" s="3">
         <v>0</v>
@@ -4456,67 +4748,73 @@
         <v>0</v>
       </c>
       <c r="H62" s="3">
+        <v>0</v>
+      </c>
+      <c r="I62" s="3">
+        <v>0</v>
+      </c>
+      <c r="J62" s="3">
         <v>1600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>1600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>1300</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O62" s="3">
         <v>18700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>14500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>11800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>10900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>7600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>6500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>6200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>5400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>5100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>5200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>8900</v>
-      </c>
-      <c r="X62" s="3">
-        <v>8400</v>
-      </c>
-      <c r="Y62" s="3">
-        <v>8100</v>
       </c>
       <c r="Z62" s="3">
         <v>8400</v>
       </c>
       <c r="AA62" s="3">
+        <v>8100</v>
+      </c>
+      <c r="AB62" s="3">
+        <v>8400</v>
+      </c>
+      <c r="AC62" s="3">
         <v>7700</v>
       </c>
     </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4592,8 +4890,14 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4669,8 +4973,14 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4746,85 +5056,97 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>73200</v>
+      </c>
+      <c r="E66" s="3">
+        <v>73200</v>
+      </c>
+      <c r="F66" s="3">
         <v>70100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>70100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>70700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>70700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>83500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>83500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>80500</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M66" s="3">
+      <c r="M66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O66" s="3">
         <v>81500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>63200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>65100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>64300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>69700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>52900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>48900</v>
-      </c>
-      <c r="T66" s="3">
-        <v>37100</v>
-      </c>
-      <c r="U66" s="3">
-        <v>38800</v>
       </c>
       <c r="V66" s="3">
         <v>37100</v>
       </c>
       <c r="W66" s="3">
+        <v>38800</v>
+      </c>
+      <c r="X66" s="3">
+        <v>37100</v>
+      </c>
+      <c r="Y66" s="3">
         <v>43200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>42900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>38800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>43100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>44200</v>
       </c>
     </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4852,8 +5174,10 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4929,8 +5253,14 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5006,8 +5336,14 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5083,8 +5419,14 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5160,85 +5502,97 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="F72" s="3">
         <v>100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>3200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>3200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-100</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O72" s="3">
         <v>49800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>48300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>45400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>44200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>43400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>41600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>41000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>41200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>39000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>36600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>33300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>33500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>31000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>28300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>25700</v>
       </c>
     </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5314,8 +5668,14 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5391,8 +5751,14 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5468,85 +5834,97 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>13400</v>
+      </c>
+      <c r="E76" s="3">
+        <v>13400</v>
+      </c>
+      <c r="F76" s="3">
         <v>17800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>17800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>20900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>20900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>12700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>12700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>13400</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L76" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M76" s="3">
+      <c r="M76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O76" s="3">
         <v>67700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>66200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>63200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>62000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>61200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>59600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>60900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>61100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>59000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>56500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>53300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>53400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>50900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>48300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>45700</v>
       </c>
     </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5622,167 +6000,185 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44104</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O80" s="2">
         <v>43921</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>43830</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>43738</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>43646</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43555</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43465</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43373</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43281</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43190</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43100</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43008</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>42916</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>42825</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>42735</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="F81" s="3">
         <v>-1500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-1500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>2000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>2000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-1400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>900</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O81" s="3">
         <v>1500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>3000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>1200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>1800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>2200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>2400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>3300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>2500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>2700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>2600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5810,8 +6206,10 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5827,8 +6225,8 @@
       <c r="G83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H83" s="3">
-        <v>100</v>
+      <c r="H83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>8</v>
@@ -5836,59 +6234,65 @@
       <c r="J83" s="3">
         <v>100</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
-      <c r="L83" s="3" t="s">
-        <v>8</v>
+      <c r="K83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L83" s="3">
+        <v>100</v>
       </c>
       <c r="M83" s="3">
+        <v>0</v>
+      </c>
+      <c r="N83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O83" s="3">
         <v>2900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>2800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>2700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>2700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>2600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>2400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>2100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>2000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>1900</v>
-      </c>
-      <c r="V83" s="3">
-        <v>1800</v>
-      </c>
-      <c r="W83" s="3">
-        <v>1800</v>
       </c>
       <c r="X83" s="3">
         <v>1800</v>
       </c>
       <c r="Y83" s="3">
+        <v>1800</v>
+      </c>
+      <c r="Z83" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AA83" s="3">
         <v>1700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>1600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5964,8 +6368,14 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6041,8 +6451,14 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6118,8 +6534,14 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6195,8 +6617,14 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6272,16 +6700,22 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>8</v>
+      <c r="D89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-600</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>8</v>
@@ -6298,59 +6732,65 @@
       <c r="J89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K89" s="3">
+      <c r="K89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M89" s="3">
         <v>2200</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O89" s="3">
         <v>-3900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>8000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>8800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>9100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>2500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>4200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-1100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>2900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>1600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>1700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>3800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>1100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>7700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>6000</v>
       </c>
     </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6378,8 +6818,10 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6404,59 +6846,65 @@
       <c r="J91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-5000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-3700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-1800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-12400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-4500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-7500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-4200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-3400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-2200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-12000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-2100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6532,8 +6980,14 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6609,16 +7063,22 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>8</v>
+      <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
+        <v>0</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>8</v>
@@ -6635,59 +7095,65 @@
       <c r="J94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K94" s="3">
+      <c r="K94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M94" s="3">
         <v>-900</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O94" s="3">
         <v>-4900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-3500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-1700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-12300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-4400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-6700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-4100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-3300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-2100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-6000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6715,8 +7181,10 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6741,11 +7209,11 @@
       <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -6792,8 +7260,14 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6869,8 +7343,14 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6946,8 +7426,14 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7023,16 +7509,22 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>8</v>
+      <c r="D100" s="3">
+        <v>300</v>
+      </c>
+      <c r="E100" s="3">
+        <v>300</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>8</v>
@@ -7049,59 +7541,65 @@
       <c r="J100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K100" s="3">
+      <c r="K100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M100" s="3">
         <v>-1200</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O100" s="3">
         <v>12600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-1800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-2000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-6800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>13500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>1500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>6100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-1500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-1600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-2700</v>
-      </c>
-      <c r="W100" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="X100" s="3">
-        <v>5700</v>
       </c>
       <c r="Y100" s="3">
         <v>-1500</v>
       </c>
       <c r="Z100" s="3">
+        <v>5700</v>
+      </c>
+      <c r="AA100" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="AB100" s="3">
         <v>-2000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-2600</v>
       </c>
     </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7117,8 +7615,8 @@
       <c r="G101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H101" s="3">
-        <v>0</v>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I101" s="3" t="s">
         <v>8</v>
@@ -7126,17 +7624,17 @@
       <c r="J101" s="3">
         <v>0</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>8</v>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L101" s="3">
+        <v>0</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
+      <c r="N101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O101" s="3">
         <v>0</v>
@@ -7177,16 +7675,22 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E102" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="F102" s="3">
         <v>0</v>
@@ -7204,54 +7708,60 @@
         <v>0</v>
       </c>
       <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
         <v>200</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O102" s="3">
         <v>3700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>2700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>5100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>3700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-2200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>3600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-6700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-2000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-1900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-1900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>8100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-6400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>3800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>1800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GV_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GV_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="92">
   <si>
     <t>GV</t>
   </si>
@@ -781,11 +781,11 @@
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
-        <v>1700</v>
-      </c>
-      <c r="E8" s="3">
-        <v>1700</v>
+      <c r="D8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F8" s="3">
         <v>2200</v>
@@ -793,11 +793,11 @@
       <c r="G8" s="3">
         <v>2200</v>
       </c>
-      <c r="H8" s="3">
-        <v>2500</v>
-      </c>
-      <c r="I8" s="3">
-        <v>2500</v>
+      <c r="H8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J8" s="3">
         <v>3300</v>
@@ -864,11 +864,11 @@
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
-        <v>1200</v>
-      </c>
-      <c r="E9" s="3">
-        <v>1200</v>
+      <c r="D9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F9" s="3">
         <v>1800</v>
@@ -876,11 +876,11 @@
       <c r="G9" s="3">
         <v>1800</v>
       </c>
-      <c r="H9" s="3">
-        <v>1600</v>
-      </c>
-      <c r="I9" s="3">
-        <v>1600</v>
+      <c r="H9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J9" s="3">
         <v>1900</v>
@@ -947,11 +947,11 @@
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3">
-        <v>400</v>
-      </c>
-      <c r="E10" s="3">
-        <v>400</v>
+      <c r="D10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F10" s="3">
         <v>400</v>
@@ -959,11 +959,11 @@
       <c r="G10" s="3">
         <v>400</v>
       </c>
-      <c r="H10" s="3">
-        <v>800</v>
-      </c>
-      <c r="I10" s="3">
-        <v>800</v>
+      <c r="H10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J10" s="3">
         <v>1400</v>
@@ -1239,11 +1239,11 @@
       <c r="G14" s="3">
         <v>100</v>
       </c>
-      <c r="H14" s="3">
-        <v>-4400</v>
-      </c>
-      <c r="I14" s="3">
-        <v>-4400</v>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J14" s="3">
         <v>100</v>
@@ -1311,10 +1311,10 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="E15" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="F15" s="3">
         <v>600</v>
@@ -1323,10 +1323,10 @@
         <v>300</v>
       </c>
       <c r="H15" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="I15" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="J15" s="3">
         <v>300</v>
@@ -1421,11 +1421,11 @@
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
-        <v>1800</v>
-      </c>
-      <c r="E17" s="3">
-        <v>1800</v>
+      <c r="D17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F17" s="3">
         <v>2400</v>
@@ -1433,11 +1433,11 @@
       <c r="G17" s="3">
         <v>2400</v>
       </c>
-      <c r="H17" s="3">
-        <v>3400</v>
-      </c>
-      <c r="I17" s="3">
-        <v>3400</v>
+      <c r="H17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J17" s="3">
         <v>2700</v>
@@ -1504,11 +1504,11 @@
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
-        <v>-100</v>
-      </c>
-      <c r="E18" s="3">
-        <v>-100</v>
+      <c r="D18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F18" s="3">
         <v>-200</v>
@@ -1516,11 +1516,11 @@
       <c r="G18" s="3">
         <v>-200</v>
       </c>
-      <c r="H18" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-1000</v>
+      <c r="H18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J18" s="3">
         <v>600</v>
@@ -1618,11 +1618,11 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>1600</v>
-      </c>
-      <c r="E20" s="3">
-        <v>1600</v>
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F20" s="3">
         <v>0</v>
@@ -1630,11 +1630,11 @@
       <c r="G20" s="3">
         <v>0</v>
       </c>
-      <c r="H20" s="3">
-        <v>-700</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-700</v>
+      <c r="H20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J20" s="3">
         <v>0</v>
@@ -1702,10 +1702,10 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-1100</v>
+        <v>0</v>
       </c>
       <c r="E21" s="3">
-        <v>-1100</v>
+        <v>0</v>
       </c>
       <c r="F21" s="3">
         <v>400</v>
@@ -1714,10 +1714,10 @@
         <v>200</v>
       </c>
       <c r="H21" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I21" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J21" s="3">
         <v>900</v>
@@ -1784,11 +1784,11 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>1200</v>
-      </c>
-      <c r="E22" s="3">
-        <v>1200</v>
+      <c r="D22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F22" s="3">
         <v>1500</v>
@@ -1796,11 +1796,11 @@
       <c r="G22" s="3">
         <v>1500</v>
       </c>
-      <c r="H22" s="3">
-        <v>1600</v>
-      </c>
-      <c r="I22" s="3">
-        <v>1600</v>
+      <c r="H22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J22" s="3">
         <v>1400</v>
@@ -1867,11 +1867,11 @@
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="E23" s="3">
-        <v>-2900</v>
+      <c r="D23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F23" s="3">
         <v>-1800</v>
@@ -1879,11 +1879,11 @@
       <c r="G23" s="3">
         <v>-1800</v>
       </c>
-      <c r="H23" s="3">
-        <v>2500</v>
-      </c>
-      <c r="I23" s="3">
-        <v>2500</v>
+      <c r="H23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J23" s="3">
         <v>-900</v>
@@ -1950,11 +1950,11 @@
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>100</v>
-      </c>
-      <c r="E24" s="3">
-        <v>100</v>
+      <c r="D24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F24" s="3">
         <v>-300</v>
@@ -1962,11 +1962,11 @@
       <c r="G24" s="3">
         <v>-300</v>
       </c>
-      <c r="H24" s="3">
-        <v>500</v>
-      </c>
-      <c r="I24" s="3">
-        <v>500</v>
+      <c r="H24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J24" s="3">
         <v>-500</v>
@@ -2116,11 +2116,11 @@
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="E26" s="3">
-        <v>-2900</v>
+      <c r="D26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F26" s="3">
         <v>-1500</v>
@@ -2128,11 +2128,11 @@
       <c r="G26" s="3">
         <v>-1500</v>
       </c>
-      <c r="H26" s="3">
-        <v>2000</v>
-      </c>
-      <c r="I26" s="3">
-        <v>2000</v>
+      <c r="H26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J26" s="3">
         <v>-400</v>
@@ -2199,11 +2199,11 @@
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="E27" s="3">
-        <v>-2900</v>
+      <c r="D27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F27" s="3">
         <v>-1500</v>
@@ -2211,11 +2211,11 @@
       <c r="G27" s="3">
         <v>-1500</v>
       </c>
-      <c r="H27" s="3">
-        <v>2000</v>
-      </c>
-      <c r="I27" s="3">
-        <v>2000</v>
+      <c r="H27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J27" s="3">
         <v>-400</v>
@@ -2614,11 +2614,11 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-1600</v>
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F32" s="3">
         <v>0</v>
@@ -2626,11 +2626,11 @@
       <c r="G32" s="3">
         <v>0</v>
       </c>
-      <c r="H32" s="3">
-        <v>700</v>
-      </c>
-      <c r="I32" s="3">
-        <v>700</v>
+      <c r="H32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J32" s="3">
         <v>0</v>
@@ -2697,11 +2697,11 @@
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="E33" s="3">
-        <v>-2900</v>
+      <c r="D33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F33" s="3">
         <v>-1500</v>
@@ -2709,11 +2709,11 @@
       <c r="G33" s="3">
         <v>-1500</v>
       </c>
-      <c r="H33" s="3">
-        <v>2000</v>
-      </c>
-      <c r="I33" s="3">
-        <v>2000</v>
+      <c r="H33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J33" s="3">
         <v>-400</v>
@@ -2863,11 +2863,11 @@
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="E35" s="3">
-        <v>-2900</v>
+      <c r="D35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F35" s="3">
         <v>-1500</v>
@@ -2875,11 +2875,11 @@
       <c r="G35" s="3">
         <v>-1500</v>
       </c>
-      <c r="H35" s="3">
-        <v>2000</v>
-      </c>
-      <c r="I35" s="3">
-        <v>2000</v>
+      <c r="H35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J35" s="3">
         <v>-400</v>
@@ -3096,11 +3096,11 @@
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
-        <v>200</v>
-      </c>
-      <c r="E41" s="3">
-        <v>200</v>
+      <c r="D41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F41" s="3">
         <v>600</v>
@@ -3108,11 +3108,11 @@
       <c r="G41" s="3">
         <v>600</v>
       </c>
-      <c r="H41" s="3">
-        <v>400</v>
-      </c>
-      <c r="I41" s="3">
-        <v>400</v>
+      <c r="H41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J41" s="3">
         <v>700</v>
@@ -3262,11 +3262,11 @@
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F43" s="3">
         <v>100</v>
@@ -3274,11 +3274,11 @@
       <c r="G43" s="3">
         <v>100</v>
       </c>
-      <c r="H43" s="3">
-        <v>300</v>
-      </c>
-      <c r="I43" s="3">
-        <v>300</v>
+      <c r="H43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J43" s="3">
         <v>300</v>
@@ -3428,11 +3428,11 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>1600</v>
-      </c>
-      <c r="E45" s="3">
-        <v>1600</v>
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F45" s="3">
         <v>1400</v>
@@ -3440,11 +3440,11 @@
       <c r="G45" s="3">
         <v>1400</v>
       </c>
-      <c r="H45" s="3">
-        <v>17100</v>
-      </c>
-      <c r="I45" s="3">
-        <v>17100</v>
+      <c r="H45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J45" s="3">
         <v>20900</v>
@@ -3511,11 +3511,11 @@
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3">
-        <v>1800</v>
-      </c>
-      <c r="E46" s="3">
-        <v>1800</v>
+      <c r="D46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F46" s="3">
         <v>2100</v>
@@ -3523,11 +3523,11 @@
       <c r="G46" s="3">
         <v>2100</v>
       </c>
-      <c r="H46" s="3">
-        <v>18300</v>
-      </c>
-      <c r="I46" s="3">
-        <v>18300</v>
+      <c r="H46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J46" s="3">
         <v>22300</v>
@@ -3606,11 +3606,11 @@
       <c r="G47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H47" s="3">
-        <v>100</v>
-      </c>
-      <c r="I47" s="3">
-        <v>100</v>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J47" s="3">
         <v>100</v>
@@ -3677,11 +3677,11 @@
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
-        <v>82800</v>
-      </c>
-      <c r="E48" s="3">
-        <v>82800</v>
+      <c r="D48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F48" s="3">
         <v>83600</v>
@@ -3689,11 +3689,11 @@
       <c r="G48" s="3">
         <v>83600</v>
       </c>
-      <c r="H48" s="3">
-        <v>68700</v>
-      </c>
-      <c r="I48" s="3">
-        <v>68700</v>
+      <c r="H48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J48" s="3">
         <v>70300</v>
@@ -3760,11 +3760,11 @@
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
-        <v>1900</v>
-      </c>
-      <c r="E49" s="3">
-        <v>1900</v>
+      <c r="D49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F49" s="3">
         <v>1900</v>
@@ -3772,11 +3772,11 @@
       <c r="G49" s="3">
         <v>1900</v>
       </c>
-      <c r="H49" s="3">
-        <v>1900</v>
-      </c>
-      <c r="I49" s="3">
-        <v>1900</v>
+      <c r="H49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J49" s="3">
         <v>1900</v>
@@ -4009,11 +4009,11 @@
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>200</v>
-      </c>
-      <c r="E52" s="3">
-        <v>200</v>
+      <c r="D52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F52" s="3">
         <v>200</v>
@@ -4021,11 +4021,11 @@
       <c r="G52" s="3">
         <v>200</v>
       </c>
-      <c r="H52" s="3">
-        <v>2600</v>
-      </c>
-      <c r="I52" s="3">
-        <v>2600</v>
+      <c r="H52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J52" s="3">
         <v>900</v>
@@ -4175,11 +4175,11 @@
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3">
-        <v>86600</v>
-      </c>
-      <c r="E54" s="3">
-        <v>86600</v>
+      <c r="D54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F54" s="3">
         <v>87900</v>
@@ -4187,11 +4187,11 @@
       <c r="G54" s="3">
         <v>87900</v>
       </c>
-      <c r="H54" s="3">
-        <v>91600</v>
-      </c>
-      <c r="I54" s="3">
-        <v>91600</v>
+      <c r="H54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J54" s="3">
         <v>96200</v>
@@ -4320,11 +4320,11 @@
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
-        <v>800</v>
-      </c>
-      <c r="E57" s="3">
-        <v>800</v>
+      <c r="D57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F57" s="3">
         <v>1200</v>
@@ -4332,11 +4332,11 @@
       <c r="G57" s="3">
         <v>1200</v>
       </c>
-      <c r="H57" s="3">
-        <v>900</v>
-      </c>
-      <c r="I57" s="3">
-        <v>900</v>
+      <c r="H57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J57" s="3">
         <v>1000</v>
@@ -4403,11 +4403,11 @@
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
-        <v>64300</v>
-      </c>
-      <c r="E58" s="3">
-        <v>64300</v>
+      <c r="D58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F58" s="3">
         <v>63200</v>
@@ -4415,11 +4415,11 @@
       <c r="G58" s="3">
         <v>63200</v>
       </c>
-      <c r="H58" s="3">
-        <v>48500</v>
-      </c>
-      <c r="I58" s="3">
-        <v>48500</v>
+      <c r="H58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J58" s="3">
         <v>53700</v>
@@ -4486,11 +4486,11 @@
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>1900</v>
-      </c>
-      <c r="E59" s="3">
-        <v>1900</v>
+      <c r="D59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F59" s="3">
         <v>2400</v>
@@ -4498,11 +4498,11 @@
       <c r="G59" s="3">
         <v>2400</v>
       </c>
-      <c r="H59" s="3">
-        <v>17000</v>
-      </c>
-      <c r="I59" s="3">
-        <v>17000</v>
+      <c r="H59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J59" s="3">
         <v>22900</v>
@@ -4569,11 +4569,11 @@
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
-        <v>70600</v>
-      </c>
-      <c r="E60" s="3">
-        <v>70600</v>
+      <c r="D60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F60" s="3">
         <v>69700</v>
@@ -4581,11 +4581,11 @@
       <c r="G60" s="3">
         <v>69700</v>
       </c>
-      <c r="H60" s="3">
-        <v>69600</v>
-      </c>
-      <c r="I60" s="3">
-        <v>69600</v>
+      <c r="H60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J60" s="3">
         <v>80500</v>
@@ -4665,10 +4665,10 @@
         <v>300</v>
       </c>
       <c r="H61" s="3">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="I61" s="3">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="J61" s="3">
         <v>1200</v>
@@ -4735,11 +4735,11 @@
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>2500</v>
-      </c>
-      <c r="E62" s="3">
-        <v>2500</v>
+      <c r="D62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F62" s="3">
         <v>0</v>
@@ -4747,11 +4747,11 @@
       <c r="G62" s="3">
         <v>0</v>
       </c>
-      <c r="H62" s="3">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3">
-        <v>0</v>
+      <c r="H62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J62" s="3">
         <v>1600</v>
@@ -5067,11 +5067,11 @@
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
-        <v>73200</v>
-      </c>
-      <c r="E66" s="3">
-        <v>73200</v>
+      <c r="D66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F66" s="3">
         <v>70100</v>
@@ -5079,11 +5079,11 @@
       <c r="G66" s="3">
         <v>70100</v>
       </c>
-      <c r="H66" s="3">
-        <v>70700</v>
-      </c>
-      <c r="I66" s="3">
-        <v>70700</v>
+      <c r="H66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J66" s="3">
         <v>83500</v>
@@ -5513,11 +5513,11 @@
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
-        <v>-5700</v>
-      </c>
-      <c r="E72" s="3">
-        <v>-5700</v>
+      <c r="D72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F72" s="3">
         <v>100</v>
@@ -5525,11 +5525,11 @@
       <c r="G72" s="3">
         <v>100</v>
       </c>
-      <c r="H72" s="3">
-        <v>3200</v>
-      </c>
-      <c r="I72" s="3">
-        <v>3200</v>
+      <c r="H72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J72" s="3">
         <v>-900</v>
@@ -5845,11 +5845,11 @@
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3">
-        <v>13400</v>
-      </c>
-      <c r="E76" s="3">
-        <v>13400</v>
+      <c r="D76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F76" s="3">
         <v>17800</v>
@@ -5857,11 +5857,11 @@
       <c r="G76" s="3">
         <v>17800</v>
       </c>
-      <c r="H76" s="3">
-        <v>20900</v>
-      </c>
-      <c r="I76" s="3">
-        <v>20900</v>
+      <c r="H76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J76" s="3">
         <v>12700</v>
@@ -6099,11 +6099,11 @@
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="E81" s="3">
-        <v>-2900</v>
+      <c r="D81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F81" s="3">
         <v>-1500</v>
@@ -6111,11 +6111,11 @@
       <c r="G81" s="3">
         <v>-1500</v>
       </c>
-      <c r="H81" s="3">
-        <v>2000</v>
-      </c>
-      <c r="I81" s="3">
-        <v>2000</v>
+      <c r="H81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J81" s="3">
         <v>-400</v>
@@ -6711,11 +6711,11 @@
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>-600</v>
-      </c>
-      <c r="E89" s="3">
-        <v>-600</v>
+      <c r="D89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>8</v>
@@ -7074,11 +7074,11 @@
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
-      </c>
-      <c r="E94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>8</v>
@@ -7520,11 +7520,11 @@
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>300</v>
-      </c>
-      <c r="E100" s="3">
-        <v>300</v>
+      <c r="D100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>8</v>
@@ -7687,10 +7687,10 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="E102" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="F102" s="3">
         <v>0</v>
